--- a/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H279"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1452,7 +1452,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.composed[1]</t>
+          <t xml:space="preserve">ahead.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1477,14 +1477,14 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めません。…この結末は</t>
+          <t xml:space="preserve">…終わった件だよ。…片付けきれてないのは、私の方か</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.composed[1]</t>
+          <t xml:space="preserve">behind.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1509,14 +1509,14 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決着がつきました。…もう十分です</t>
+          <t xml:space="preserve">…終わったって言われてる。…受け取れてないだけだよ</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けました。でもこの試合は忘れません。…ありがとう</t>
+          <t xml:space="preserve">…認めません。…この結末は</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
@@ -1573,14 +1573,14 @@
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あなたのおかげでここまで来れた。…これからも、よろしく</t>
+          <t xml:space="preserve">…決着がつきました。…もう十分です</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">loser.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1605,14 +1605,14 @@
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで終わらせます</t>
+          <t xml:space="preserve">…負けました。でもこの試合は忘れません。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.composed[1]</t>
+          <t xml:space="preserve">winner.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1637,14 +1637,14 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力でお相手します</t>
+          <t xml:space="preserve">…あなたのおかげでここまで来れた。…これからも、よろしく</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
@@ -1669,14 +1669,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全てを賭けます</t>
+          <t xml:space="preserve">…ここで終わらせます</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい。全力で</t>
+          <t xml:space="preserve">…全力でお相手します</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
@@ -1733,14 +1733,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決着をつけます。今日で</t>
+          <t xml:space="preserve">…全てを賭けます</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
@@ -1765,14 +1765,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…受けて立ちます。全力で</t>
+          <t xml:space="preserve">…はい。全力で</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.earnest.composed[1]</t>
+          <t xml:space="preserve">attacker.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1797,14 +1797,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日で終わりにします</t>
+          <t xml:space="preserve">…決着をつけます。今日で</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.earnest.composed[1]</t>
+          <t xml:space="preserve">defender.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1829,14 +1829,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力で受けます</t>
+          <t xml:space="preserve">…受けて立ちます。全力で</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けました。…でも、次は</t>
+          <t xml:space="preserve">…今日で終わりにします</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.composed[1]</t>
+          <t xml:space="preserve">fateDefender.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1893,14 +1893,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝ちました。でもまだ続きます</t>
+          <t xml:space="preserve">…全力で受けます</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.earnest.composed[1]</t>
+          <t xml:space="preserve">loserLines.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1925,14 +1925,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けました。…でも、ここからです</t>
+          <t xml:space="preserve">…負けました。…でも、次は</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.earnest.composed[1]</t>
+          <t xml:space="preserve">winnerLines.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1957,14 +1957,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…長かった。一つ答えが出た。…でも、まだ先がある</t>
+          <t xml:space="preserve">…勝ちました。でもまだ続きます</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.composed[1]</t>
+          <t xml:space="preserve">fateLoser.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1989,14 +1989,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けました。…でも、次は変えてみせます</t>
+          <t xml:space="preserve">…負けました。…でも、ここからです</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.composed[1]</t>
+          <t xml:space="preserve">fateWinner.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2021,14 +2021,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ決着がつきました。…でもまだ、先がある気がします</t>
+          <t xml:space="preserve">…長かった。一つ答えが出た。…でも、まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.composed[1]</t>
+          <t xml:space="preserve">loser.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2053,14 +2053,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなはずでは。…なぜ</t>
+          <t xml:space="preserve">…負けました。…でも、次は変えてみせます</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.composed[1]</t>
+          <t xml:space="preserve">winner.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2085,14 +2085,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと追いかけてきた。…ようやく、届いた</t>
+          <t xml:space="preserve">…一つ決着がつきました。…でもまだ、先がある気がします</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.earnest.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.earnest.composed[1]</t>
+          <t xml:space="preserve">loserLines.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2117,14 +2117,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が{nameA}を真っ直ぐ見た。「…もう十分待った。…本気で行きます」</t>
+          <t xml:space="preserve">…こんなはずでは。…なぜ</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2134,29 +2134,29 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.lose[1]</t>
+          <t xml:space="preserve">winnerLines.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。…わがままを通した挙句、この結果です。申し訳ありません。</t>
+          <t xml:space="preserve">…ずっと追いかけてきた。…ようやく、届いた</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.lose[2]</t>
+          <t xml:space="preserve">awakening.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗です。…社長の判断を、無駄にしました。</t>
+          <t xml:space="preserve">{nameB}が{nameA}を真っ直ぐ見た。「…もう十分待った。…本気で行きます」</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.lose[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.lose[3]</t>
+          <t xml:space="preserve">composed_earnest.lose[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2213,14 +2213,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すみません。頼み込んだのは自分なのに、勝てませんでした。</t>
+          <t xml:space="preserve">負けました。…わがままを通した挙句、この結果です。申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.lose[2]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.petition[1]</t>
+          <t xml:space="preserve">composed_earnest.lose[2]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2245,14 +2245,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…あの人と、やらせてください。覚悟はできています。</t>
+          <t xml:space="preserve">完敗です。…社長の判断を、無駄にしました。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.lose[3]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.petition[2]</t>
+          <t xml:space="preserve">composed_earnest.lose[3]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2277,14 +2277,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わがままを言います。あの人と、やらせてください。責任は取ります。</t>
+          <t xml:space="preserve">…すみません。頼み込んだのは自分なのに、勝てませんでした。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.petition[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.petition[3]</t>
+          <t xml:space="preserve">composed_earnest.petition[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…自分に必要な相手です。あの人と、お願いします。</t>
+          <t xml:space="preserve">社長。…あの人と、やらせてください。覚悟はできています。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.petition[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.sendoff[1]</t>
+          <t xml:space="preserve">composed_earnest.petition[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2341,14 +2341,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。…託された分、務めてきます。</t>
+          <t xml:space="preserve">…わがままを言います。あの人と、やらせてください。責任は取ります。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.petition[3]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.sendoff[2]</t>
+          <t xml:space="preserve">composed_earnest.petition[3]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2373,14 +2373,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…背中を押していただきました。恥じない試合をしてきます。</t>
+          <t xml:space="preserve">社長。…自分に必要な相手です。あの人と、お願いします。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.sendoff[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.sendoff[3]</t>
+          <t xml:space="preserve">composed_earnest.sendoff[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2405,14 +2405,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝します。…行ってきます。無駄には、しません。</t>
+          <t xml:space="preserve">ありがとうございます。…託された分、務めてきます。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.sendoff[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.win[1]</t>
+          <t xml:space="preserve">composed_earnest.sendoff[2]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2437,14 +2437,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。…社長、任せていただいた甲斐がありました。</t>
+          <t xml:space="preserve">…背中を押していただきました。恥じない試合をしてきます。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.sendoff[3]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.win[2]</t>
+          <t xml:space="preserve">composed_earnest.sendoff[3]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2469,14 +2469,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…役目は果たせました。ありがとうございます。</t>
+          <t xml:space="preserve">感謝します。…行ってきます。無駄には、しません。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.win[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.win[3]</t>
+          <t xml:space="preserve">composed_earnest.win[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。…言い出した責任は、これで返せたでしょうか。</t>
+          <t xml:space="preserve">勝ちました。…社長、任せていただいた甲斐がありました。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.win[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest._accept[1]</t>
+          <t xml:space="preserve">composed_earnest.win[2]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2533,14 +2533,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受ける。呼ばれたら、応えるのが筋だ。</t>
+          <t xml:space="preserve">…役目は果たせました。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_earnest.win[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest._accept[2]</t>
+          <t xml:space="preserve">composed_earnest.win[3]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2565,14 +2565,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかった。……半端な向き合い方はしない。</t>
+          <t xml:space="preserve">勝てました。…言い出した責任は、これで返せたでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest._accept[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest._accept[3]</t>
+          <t xml:space="preserve">composed_earnest._accept[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2597,14 +2597,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいだろう。その覚悟、正面から受け取る。</t>
+          <t xml:space="preserve">……受ける。呼ばれたら、応えるのが筋だ。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest._accept[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.draw[1]</t>
+          <t xml:space="preserve">composed_earnest._accept[2]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2629,14 +2629,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着をつけられなかった。それが心残りだ。</t>
+          <t xml:space="preserve">わかった。……半端な向き合い方はしない。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest._accept[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.draw[2]</t>
+          <t xml:space="preserve">composed_earnest._accept[3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2661,14 +2661,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けでは、答えたことにならない。</t>
+          <t xml:space="preserve">……いいだろう。その覚悟、正面から受け取る。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.draw[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.draw[3]</t>
+          <t xml:space="preserve">composed_earnest.draw[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2693,14 +2693,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ途中だ。必ず、続きをやろう。</t>
+          <t xml:space="preserve">……決着をつけられなかった。それが心残りだ。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.draw[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.lose[1]</t>
+          <t xml:space="preserve">composed_earnest.draw[2]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2725,14 +2725,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受けておいて、この結果か。情けない。</t>
+          <t xml:space="preserve">これでは、答えたことにならない。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.draw[3]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.lose[2]</t>
+          <t xml:space="preserve">composed_earnest.draw[3]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたが上だった。……言い訳はしない。</t>
+          <t xml:space="preserve">……まだ途中だ。必ず、続きをやろう。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.lose[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.lose[3]</t>
+          <t xml:space="preserve">composed_earnest.lose[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2789,14 +2789,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けは、わたしのものだ。持って帰るよ。</t>
+          <t xml:space="preserve">……受けておいて、この結果か。情けない。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.lose[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.win[1]</t>
+          <t xml:space="preserve">composed_earnest.lose[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2821,14 +2821,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……務めは果たした。あんたも、よくやったよ。</t>
+          <t xml:space="preserve">あんたが上だった。……言い訳はしない。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.lose[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.win[2]</t>
+          <t xml:space="preserve">composed_earnest.lose[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2853,14 +2853,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けた以上、負けるわけにはいかなかった。</t>
+          <t xml:space="preserve">……負けは、わたしのものだ。持って帰るよ。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.win[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_earnest.win[3]</t>
+          <t xml:space="preserve">composed_earnest.win[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2885,14 +2885,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ったよ。重い一戦だった。</t>
+          <t xml:space="preserve">……務めは果たした。あんたも、よくやったよ。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.earnest.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.win[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2902,29 +2902,29 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.earnest.composed[1]</t>
+          <t xml:space="preserve">composed_earnest.win[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。…まだやれることがあるなら、続けるよ</t>
+          <t xml:space="preserve">受けた以上、負けるわけにはいかなかった。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_earnest.win[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2934,29 +2934,29 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">composed_earnest.win[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後にもう一度。…あのベルトに恥じない闘いをしたい</t>
+          <t xml:space="preserve">……勝ったよ。重い一戦だった。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.earnest.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.earnest.composed[1]</t>
+          <t xml:space="preserve">accepted.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。…まだ役に立てるなら、やるよ</t>
+          <t xml:space="preserve">…ここで学んだこと、ちゃんと活かすよ。…世話になったね</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.composed[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.earnest.composed[1]</t>
+          <t xml:space="preserve">accepted.earnest.composed[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3013,14 +3013,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…信じてくれてありがとう。…期待には応えるよ</t>
+          <t xml:space="preserve">…感謝しかない。向こうで結果を出す</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">defended.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3045,14 +3045,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後にいい試合を。…それだけでいい</t>
+          <t xml:space="preserve">…社長の気持ち、伝わったよ。…ここで闘い続ける</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.composed[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">defended.earnest.composed[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3077,14 +3077,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後まで演じきれたなら、悪くない。…わかった</t>
+          <t xml:space="preserve">…残らせてもらう。恩は必ず返すよ</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.earnest.composed[1]</t>
+          <t xml:space="preserve">defense_failed.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚悟はできてた。…ありがとう、言ってくれて</t>
+          <t xml:space="preserve">…恩を返せないままだね。…新天地で必ず結果を出すよ</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.composed[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.earnest.composed[1]</t>
+          <t xml:space="preserve">defense_failed.earnest.composed[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3141,14 +3141,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。言ってくれて。…助かった</t>
+          <t xml:space="preserve">…ごめん。…でも、行かなきゃいけないんだ</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.earnest.composed[1]</t>
+          <t xml:space="preserve">default.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3173,14 +3173,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと早く気づくべきだった。…わかった</t>
+          <t xml:space="preserve">…わかった。…まだやれることがあるなら、続けるよ</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">former_champ.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3205,14 +3205,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このベルトの重み、まだ背負える。…引退はしないよ</t>
+          <t xml:space="preserve">…最後にもう一度。…あのベルトに恥じない闘いをしたい</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.earnest.composed[1]</t>
+          <t xml:space="preserve">heel.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この団体のために尽くしてきた。…それは嘘じゃない</t>
+          <t xml:space="preserve">…わかった。…まだ役に立てるなら、やるよ</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.earnest.composed[1]</t>
+          <t xml:space="preserve">high_trust.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3269,14 +3269,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだやれることがある。…ここで止まるわけにはいかない</t>
+          <t xml:space="preserve">…信じてくれてありがとう。…期待には応えるよ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3301,14 +3301,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次の興行で証明する。…後悔させてあげるよ</t>
+          <t xml:space="preserve">…最後にいい試合を。…それだけでいい</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_heel.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3333,14 +3333,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…恥じることは何もないよ。…うん、十分だ</t>
+          <t xml:space="preserve">…最後まで演じきれたなら、悪くない。…わかった</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3365,14 +3365,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嘘はなかった。…それで十分だよ</t>
+          <t xml:space="preserve">…覚悟はできてた。…ありがとう、言ってくれて</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3397,14 +3397,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…誰かがやらなきゃいけなかった。…それだけだよ</t>
+          <t xml:space="preserve">…ありがとう。言ってくれて。…助かった</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_winless.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3429,14 +3429,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嘘のない時間だった。…それだけで十分だよ</t>
+          <t xml:space="preserve">…もっと早く気づくべきだった。…わかった</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.earnest.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3461,14 +3461,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ何も返せてない。…こんなの、困るよ</t>
+          <t xml:space="preserve">…このベルトの重み、まだ背負える。…引退はしないよ</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.earnest.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3493,14 +3493,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっとやりたかった。…それだけだよ</t>
+          <t xml:space="preserve">…この団体のために尽くしてきた。…それは嘘じゃない</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.earnest.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3525,14 +3525,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔いがないとは言わない。…でも、やりきったよ</t>
+          <t xml:space="preserve">…まだやれることがある。…ここで止まるわけにはいかない</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.earnest.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後の防衛戦、やりたかったな。…それだけだよ</t>
+          <t xml:space="preserve">…次の興行で証明する。…後悔させてあげるよ</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">A1_champion.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…来年もよろしく。やれることをやるだけだよ</t>
+          <t xml:space="preserve">…恥じることは何もないよ。…うん、十分だ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.earnest.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。この評価に…恥じない結果を出します。</t>
+          <t xml:space="preserve">…嘘はなかった。…それで十分だよ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3638,29 +3638,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.earnest.composed[1]</t>
+          <t xml:space="preserve">A3_heel.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。社長の判断なら…受け入れるよ。やれることをやる。</t>
+          <t xml:space="preserve">…誰かがやらなきゃいけなかった。…それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3670,29 +3670,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.earnest.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…残念ですが…了解です。ただ…この判断は、忘れないでください。</t>
+          <t xml:space="preserve">…嘘のない時間だった。…それだけで十分だよ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3702,29 +3702,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest.composed[1]</t>
+          <t xml:space="preserve">B1_young.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、筋を通させてください。{tenure}{record}…落ち着いて考えた結論です。</t>
+          <t xml:space="preserve">…まだ何も返せてない。…こんなの、困るよ</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3734,29 +3734,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.earnest.composed[1]</t>
+          <t xml:space="preserve">B2_prime.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。ただ…このままでは、いずれ動くことになる。それだけです。</t>
+          <t xml:space="preserve">…もっとやりたかった。…それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3766,29 +3766,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest.composed[1]</t>
+          <t xml:space="preserve">B3_older.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}ここでの時間は…悪くなかった。ただ…次に進むべきだと思ってます。</t>
+          <t xml:space="preserve">…悔いがないとは言わない。…でも、やりきったよ</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3798,577 +3798,577 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長の誠意は…伝わりました。もう一度…やってみます。</t>
+          <t xml:space="preserve">…最後の防衛戦、やりたかったな。…それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…来年もよろしく。やれることをやるだけだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_accept.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。この評価に…恥じない結果を出します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_accept.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…なるほど。社長の判断なら…受け入れるよ。やれることをやる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_refuse.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…残念ですが…了解です。ただ…この判断は、忘れないでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_open.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、筋を通させてください。{tenure}{record}…落ち着いて考えた結論です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…承知しました。ただ…このままでは、いずれ動くことになる。それだけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。長い間、世話になったね。…でも、もうここでは続けられない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ずっと考えてきたことでね。…ここを、去ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとう。{record}自分なりに考えた結論でね。ここでの経験には感謝してる。…ただ、新しい場所で試したいんだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}ここでの時間は…悪くなかった。ただ…次に進むべきだと思ってます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…承知しました。{tenure_farewell}ここで過ごした日々は…忘れないよ。{rivalry}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…気持ちはありがたい。…ただ、これは長く考えた末の結論でね。…申し訳ない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長の誠意は…伝わりました。もう一度…やってみます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr" s="2">
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr" s="12">
+      <c r="D123" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr" s="2">
+      <c r="E123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr" s="3">
+      <c r="F123" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…今の仲間への責任がある。
 それを放り出すわけにはいかない</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="40" customHeight="1">
-      <c r="A111" t="inlineStr" s="15">
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr" s="2">
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr" s="12">
+      <c r="D124" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr" s="2">
+      <c r="E124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr" s="3">
+      <c r="F124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…みんなを置いてはいけない。
 …ごめん</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="40" customHeight="1">
-      <c r="A112" t="inlineStr" s="15">
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr" s="2">
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr" s="12">
+      <c r="D125" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr" s="2">
+      <c r="E125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr" s="3">
+      <c r="F125" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…この団体を離れるのは簡単じゃない。
 …でも、聞くだけなら</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="40" customHeight="1">
-      <c r="A113" t="inlineStr" s="15">
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr" s="2">
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr" s="12">
+      <c r="D126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr" s="2">
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…新しい場所で、やるべきことをやる。
 よろしく</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="40" customHeight="1">
-      <c r="A114" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのメンバーのこと、いま少しお気にかけていただきたいのですが。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="40" customHeight="1">
-      <c r="A115" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次の興行のメインを私たちに任せていただけないか、ご検討いただけますか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="40" customHeight="1">
-      <c r="A116" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのメンバーの待遇について、一度ご検討いただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="40" customHeight="1">
-      <c r="A117" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの貢献に、一言いただける機会をお願いしたいのですが。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="40" customHeight="1">
-      <c r="A118" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ありがとうございます。お言葉、しっかり受け取ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="40" customHeight="1">
-      <c r="A119" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、ご配慮ありがとうございます。お気持ち、しっかり受け取ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="40" customHeight="1">
-      <c r="A121" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ありがとうございます。お預かりした以上、形にしてお返しします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。次回、改めてお願いします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ありがとうございます。お気持ち、しっかり受け取ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。みんなを代表して、お礼を申し上げます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。お時間を取らせてしまい、すみませんでした。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、ご配慮ありがとうございます。気持ち、しっかり受け取ります。</t>
-        </is>
-      </c>
-    </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4393,14 +4393,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。お言葉、しっかり受け取ります。</t>
+          <t xml:space="preserve">社長、私たちのメンバーのこと、いま少しお気にかけていただきたいのですが。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4425,14 +4425,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
+          <t xml:space="preserve">社長、次の興行のメインを私たちに任せていただけないか、ご検討いただけますか。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4457,14 +4457,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮ありがとうございます。お気持ち、しっかり受け取ります。</t>
+          <t xml:space="preserve">社長、私たちのメンバーの待遇について、一度ご検討いただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。輪の外にいる子の気持ち、見えていませんでした。</t>
+          <t xml:space="preserve">社長、私たちの貢献に、一言いただける機会をお願いしたいのですが。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎないように気をつけます。</t>
+          <t xml:space="preserve">ありがとうございます。お言葉、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4553,14 +4553,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません、配慮が足りませんでした。</t>
+          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4585,14 +4585,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…社長、ご配慮ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。リングの外まで持ち込んだのは行きすぎでした。</t>
+          <t xml:space="preserve">ありがとうございます。お預かりした以上、形にしてお返しします。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4649,14 +4649,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
+          <t xml:space="preserve">…承知しました。次回、改めてお願いします。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4681,14 +4681,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。立場をわきまえず、恥ずかしい限りです。</t>
+          <t xml:space="preserve">…ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。お見逃しいただいた分、必ず返します。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。みんなを代表して、お礼を申し上げます。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長が補ってくださる形で。</t>
+          <t xml:space="preserve">…承知しました。お時間を取らせてしまい、すみませんでした。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4777,14 +4777,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。ご厚意に、甘えさせていただきます。</t>
+          <t xml:space="preserve">…社長、ご配慮ありがとうございます。気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てます。</t>
+          <t xml:space="preserve">ありがとうございます。お言葉、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4841,14 +4841,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。チームで支えていただけると、持ち直せます。</t>
+          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の目が届いていませんでした。</t>
+          <t xml:space="preserve">…社長、ご配慮ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。穏便に収まるよう努めます。</t>
+          <t xml:space="preserve">…申し訳ありません。輪の外にいる子の気持ち、見えていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長に補っていただいて。</t>
+          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎないように気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の管理不行き届きでした。</t>
+          <t xml:space="preserve">…申し訳ありません、配慮が足りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（唇を結び、わずかに頭を下げた）</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長に拾っていただいて。</t>
+          <t xml:space="preserve">…申し訳ありません。リングの外まで持ち込んだのは行きすぎでした。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の判断が行きすぎていました。</t>
+          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。責任は私が持ちます。</t>
+          <t xml:space="preserve">…申し訳ありません。立場をわきまえず、恥ずかしい限りです。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。私が見落としていた負担を、社長に拾っていただいて。</t>
+          <t xml:space="preserve">…ありがとうございます。お見逃しいただいた分、必ず返します。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.attack.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">けじめを、つけさせてもらう</t>
+          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長が補ってくださる形で。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.defend.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるつもりはない</t>
+          <t xml:space="preserve">…ありがとうございます。ご厚意に、甘えさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5210,29 +5210,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ようやく。…まだ上がある</t>
+          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5242,29 +5242,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…あの練習が…ここで繋がった——）</t>
+          <t xml:space="preserve">…ありがとうございます。チームで支えていただけると、持ち直せます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5274,29 +5274,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…限界か。…でもここまでの道のりは、全部本物だよ</t>
+          <t xml:space="preserve">…申し訳ありません。私の目が届いていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5306,29 +5306,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来たけど、まだ終わりじゃない。…いや、始まりだよ</t>
+          <t xml:space="preserve">…ありがとうございます。穏便に収まるよう努めます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5338,29 +5338,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやってきた成果が、ちゃんと出てるね</t>
+          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長に補っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5370,29 +5370,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やれるだけのことは、やった。…でも、まだやれる</t>
+          <t xml:space="preserve">…申し訳ありません。私の管理不行き届きでした。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5402,29 +5402,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてる人がいるなら、もっと頑張らないと</t>
+          <t xml:space="preserve">（唇を結び、わずかに頭を下げた）</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5434,29 +5434,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来れたのは、見てくれた人がいたから。…恩返ししないと</t>
+          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長に拾っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5466,29 +5466,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…道場に来ても、何も返ってこない。…そういう時期か</t>
+          <t xml:space="preserve">…申し訳ありません。私の判断が行きすぎていました。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5498,29 +5498,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…闘う理由、思い出した。…もう迷わないよ</t>
+          <t xml:space="preserve">…ありがとうございます。責任は私が持ちます。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5530,29 +5530,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…待たせた分、返していくよ。…焦らずにね</t>
+          <t xml:space="preserve">…ありがとうございます。私が見落としていた負担を、社長に拾っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.composed[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.composed</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5562,29 +5562,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.attack.composed</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何が足りなかったのか。…まだ答えが出ない</t>
+          <t xml:space="preserve">けじめを、つけさせてもらう</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.composed[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.composed</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5594,29 +5594,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.defend.composed</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…復帰はできた。…でもまだ、足りない</t>
+          <t xml:space="preserve">逃げるつもりはない</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…復帰できた。…でも体は覚えてるね、あの痛みを</t>
+          <t xml:space="preserve">…積み重ねてきたものが、ようやく。…まだ上がある</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5673,14 +5673,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…怪我は治った。でも離れていた時間が…少し重い</t>
+          <t xml:space="preserve">（…あの練習が…ここで繋がった——）</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">fresh.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、あの試合で全部出せた。それだけだよ</t>
+          <t xml:space="preserve">…今日はなんだか感覚が良い。こういう日を、無駄にしたくない</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5722,29 +5722,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.composed[1]</t>
+          <t xml:space="preserve">heavy.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…毎試合、ベストを出す。それが王者の仕事だろうね</t>
+          <t xml:space="preserve">…今日は流れるだけだね。…私の頑張り方が雑なのかな</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5754,29 +5754,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest.composed[1]</t>
+          <t xml:space="preserve">warm.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩たちへ。…焦らなくていい。やるべきことをやれば、ちゃんと届くから</t>
+          <t xml:space="preserve">…積めてはいる。…厚みが出ないのが引っかかるね</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5786,29 +5786,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest.composed[1]</t>
+          <t xml:space="preserve">cap_reached.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…毎日の積み重ねが形になった。…ここで満足はしないけどね</t>
+          <t xml:space="preserve">…限界か。…でもここまでの道のりは、全部本物だよ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5818,29 +5818,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.earnest.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やることはやってきた。この賞が証明してくれたかな</t>
+          <t xml:space="preserve">…ここまで来たけど、まだ終わりじゃない。…いや、始まりだよ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5850,29 +5850,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングで、積み重ねてきたすべてを出します</t>
+          <t xml:space="preserve">…コツコツやってきた成果が、ちゃんと出てるね</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5882,29 +5882,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">ovr_legend.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">準備は、万全です</t>
+          <t xml:space="preserve">…やれるだけのことは、やった。…でも、まだやれる</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.composed[3]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5914,29 +5914,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[3]</t>
+          <t xml:space="preserve">pop_growth.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦、絶対に勝ちます</t>
+          <t xml:space="preserve">…見てくれてる人がいるなら、もっと頑張らないと</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5946,29 +5946,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">pop_star.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員達成。事実を、しっかり受け止めます</t>
+          <t xml:space="preserve">…ここまで来れたのは、見てくれた人がいたから。…恩返ししないと</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5978,29 +5978,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の声援、次への糧とします</t>
+          <t xml:space="preserve">…道場に来ても、何も返ってこない。…そういう時期か</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.composed[3]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6010,29 +6010,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[3]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精進を続けます。これで終わりではない</t>
+          <t xml:space="preserve">…闘う理由、思い出した。…もう迷わないよ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6042,29 +6042,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…地道にやるのが一番だよ。急がず行こう</t>
+          <t xml:space="preserve">…待たせた分、返していくよ。…焦らずにね</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6074,29 +6074,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest.composed[1]</t>
+          <t xml:space="preserve">defeat.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人がいると、自然と力が出るね</t>
+          <t xml:space="preserve">…何が足りなかったのか。…まだ答えが出ない</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6106,29 +6106,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休めば大丈夫。焦ることはないよ</t>
+          <t xml:space="preserve">…復帰はできた。…でもまだ、足りない</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6138,29 +6138,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest.composed[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなの声、ちゃんと届いてるよ。ありがたいね</t>
+          <t xml:space="preserve">…復帰できた。…でも体は覚えてるね、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6170,29 +6170,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest.composed[1]</t>
+          <t xml:space="preserve">penalty_end.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嫌いになったわけじゃない。ただ……ね</t>
+          <t xml:space="preserve">…怪我は治った。でも離れていた時間が…少し重い</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest.composed[1]</t>
+          <t xml:space="preserve">bestMatch.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何かが噛み合わない。…まあ、そういう時期もあるか</t>
+          <t xml:space="preserve">…積み重ねてきたものが、あの試合で全部出せた。それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">champion.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで積み重ねてきたものが、繋がった</t>
+          <t xml:space="preserve">…毎試合、ベストを出す。それが王者の仕事だろうね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…結果で示すしかないか</t>
+          <t xml:space="preserve">後輩たちへ。…焦らなくていい。やるべきことをやれば、ちゃんと届くから</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6298,29 +6298,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">mvp.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正当な評価だろうね。…でも、自分もまだ</t>
+          <t xml:space="preserve">…毎日の積み重ねが形になった。…ここで満足はしないけどね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6330,29 +6330,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">rookie.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…焦ってはいない。…でも、待つのも限度がある</t>
+          <t xml:space="preserve">…やることはやってきた。この賞が証明してくれたかな</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる。…いつでもね</t>
+          <t xml:space="preserve">ドームのリングで、積み重ねてきたすべてを出します</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.composed[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し歩み寄った方がいいのかな</t>
+          <t xml:space="preserve">準備は、万全です</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.earnest.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.composed[3]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[3]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{name2}。…ありがとう。…元気でね</t>
+          <t xml:space="preserve">この一戦、絶対に勝ちます</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやった。…それだけ</t>
+          <t xml:space="preserve">満員達成。事実を、しっかり受け止めます</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.composed[2]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6490,29 +6490,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[2]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足りないか。…次までに詰めるよ</t>
+          <t xml:space="preserve">お客様の声援、次への糧とします</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.composed[3]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6522,29 +6522,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[3]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなの分も、背負えた。…よかった</t>
+          <t xml:space="preserve">精進を続けます。これで終わりではない</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest.composed[1]</t>
+          <t xml:space="preserve">N1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいね。次で応えるよ</t>
+          <t xml:space="preserve">…地道にやるのが一番だよ。急がず行こう</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest.composed[1]</t>
+          <t xml:space="preserve">N2.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなでやれるのはいいね。じっくり行こう</t>
+          <t xml:space="preserve">…あの人がいると、自然と力が出るね</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest.composed[1]</t>
+          <t xml:space="preserve">N3.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと見てくれてたんだ。…ありがとう。応えるよ</t>
+          <t xml:space="preserve">…少し休めば大丈夫。焦ることはないよ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest.composed[1]</t>
+          <t xml:space="preserve">N4.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…その言葉、ありがたいよ。もう少し踏ん張ってみる</t>
+          <t xml:space="preserve">…みんなの声、ちゃんと届いてるよ。ありがたいね</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest.composed[1]</t>
+          <t xml:space="preserve">N5_low.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつも通りやればいいよ。大丈夫</t>
+          <t xml:space="preserve">…嫌いになったわけじゃない。ただ……ね</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6714,29 +6714,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest.composed[1]</t>
+          <t xml:space="preserve">N5_warning.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お疲れ様。こういう時間があるから、また頑張れるね</t>
+          <t xml:space="preserve">…何かが噛み合わない。…まあ、そういう時期もあるか</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6746,29 +6746,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest.composed[1]</t>
+          <t xml:space="preserve">breakthrough.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、たまには休むのも大事だよね。ありがとう</t>
+          <t xml:space="preserve">…ここで積み重ねてきたものが、繋がった</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6778,29 +6778,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.earnest.composed[1]</t>
+          <t xml:space="preserve">G1.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまでしてくれるんだ。早く戻って返すよ</t>
+          <t xml:space="preserve">…結果で示すしかないか</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest.composed[1]</t>
+          <t xml:space="preserve">G2.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいね。全部吸収させてもらうよ</t>
+          <t xml:space="preserve">…正当な評価だろうね。…でも、自分もまだ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6842,29 +6842,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.earnest.composed[1]</t>
+          <t xml:space="preserve">G3.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…緊張はしないよ。いつも通りやればいい</t>
+          <t xml:space="preserve">…焦ってはいない。…でも、待つのも限度がある</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest.composed[1]</t>
+          <t xml:space="preserve">G4.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…義理があるから断ったよ。でも、一応報告だけね</t>
+          <t xml:space="preserve">…準備はできてる。…いつでもね</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6906,29 +6906,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest.composed[1]</t>
+          <t xml:space="preserve">R2.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる。あとはチャンスだけだよ</t>
+          <t xml:space="preserve">…もう少し歩み寄った方がいいのかな</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6938,29 +6938,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.earnest.composed[1]</t>
+          <t xml:space="preserve">R3.modal.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人を越えないと先に進めない。頼むよ</t>
+          <t xml:space="preserve">…{name2}。…ありがとう。…元気でね</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6970,29 +6970,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest.composed[1]</t>
+          <t xml:space="preserve">R4.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無理したくないんだ。少し休ませてもらえるかな</t>
+          <t xml:space="preserve">…やるべきことをやった。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7002,29 +7002,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest.composed[1]</t>
+          <t xml:space="preserve">R5.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと黙ってたけど、そろそろ限界だよ</t>
+          <t xml:space="preserve">…まだ足りないか。…次までに詰めるよ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7034,29 +7034,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.earnest.composed[1]</t>
+          <t xml:space="preserve">warVictory.voice.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ伸びしろはあるはずなんだ。やらせてほしい</t>
+          <t xml:space="preserve">…みんなの分も、背負えた。…よかった</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest.composed[1]</t>
+          <t xml:space="preserve">bonus.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7081,14 +7081,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次の世代に繋げたいものがあるんだ。やらせてほしい</t>
+          <t xml:space="preserve">…ありがたいね。次で応えるよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7098,12 +7098,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.earnest.composed[1]</t>
+          <t xml:space="preserve">camp.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7113,14 +7113,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…不注意だったね。きちんと治して、ちゃんと戻るよ</t>
+          <t xml:space="preserve">…みんなでやれるのはいいね。じっくり行こう</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest.composed[1]</t>
+          <t xml:space="preserve">encourage_high_trust.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7145,14 +7145,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無理に合わせても仕方ないからね。整理してもらえると助かるよ</t>
+          <t xml:space="preserve">…ずっと見てくれてたんだ。…ありがとう。応えるよ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest.composed[1]</t>
+          <t xml:space="preserve">encourage.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7177,14 +7177,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…迷惑はかけたくないんだけどね。うまくいかないものだね</t>
+          <t xml:space="preserve">…その言葉、ありがたいよ。もう少し踏ん張ってみる</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.earnest.composed[1]</t>
+          <t xml:space="preserve">faction_decree.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちゃんとやるよ。恥ずかしくない仕事をしたいからね</t>
+          <t xml:space="preserve">……どこで間違えたのかは、自分で考えるよ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.earnest.composed[1]</t>
+          <t xml:space="preserve">media.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7241,14 +7241,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…丁寧にやるよ。せっかくの機会だからね</t>
+          <t xml:space="preserve">…いつも通りやればいいよ。大丈夫</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.earnest.composed[1]</t>
+          <t xml:space="preserve">party.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7273,14 +7273,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…落ち着いて話せばいいよね。焦らずやるよ</t>
+          <t xml:space="preserve">…お疲れ様。こういう時間があるから、また頑張れるね</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.earnest.composed[1]</t>
+          <t xml:space="preserve">refresh_leave.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7305,14 +7305,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、私でいいんだ。悪くない話だね</t>
+          <t xml:space="preserve">…まあ、たまには休むのも大事だよね。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7322,29 +7322,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">special_treatment.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
+          <t xml:space="preserve">…そこまでしてくれるんだ。早く戻って返すよ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7354,29 +7354,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">trainer.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
+          <t xml:space="preserve">…ありがたいね。全部吸収させてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7386,29 +7386,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">E1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
+          <t xml:space="preserve">…緊張はしないよ。いつも通りやればいい</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7418,29 +7418,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">E6.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
+          <t xml:space="preserve">…義理があるから断ったよ。でも、一応報告だけね</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7450,29 +7450,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">S_boycott.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
+          <t xml:space="preserve">…すまない。今日はどうにも体が動かなくてさ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.composed[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7482,29 +7482,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest.composed[1]</t>
+          <t xml:space="preserve">S_boycott.earnest.composed[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
+          <t xml:space="preserve">…集中できないんだ。…悪いね</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7514,29 +7514,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.composed[1]</t>
+          <t xml:space="preserve">S_grumble.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
+          <t xml:space="preserve">（「…このままでいいのかな」と、後輩相手に珍しく弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7546,29 +7546,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest.composed[1]</t>
+          <t xml:space="preserve">S_sns.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
+          <t xml:space="preserve">（SNSに「…私はここで必要とされてるのかな」と、珍しく率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7578,29 +7578,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest.composed[1]</t>
+          <t xml:space="preserve">S1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
+          <t xml:space="preserve">…準備はできてる。あとはチャンスだけだよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7610,29 +7610,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.composed[1]</t>
+          <t xml:space="preserve">S2.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
+          <t xml:space="preserve">…あの人を越えないと先に進めない。頼むよ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7642,29 +7642,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.composed[1]</t>
+          <t xml:space="preserve">S3.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
+          <t xml:space="preserve">…無理したくないんだ。少し休ませてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7674,29 +7674,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest.composed[1]</t>
+          <t xml:space="preserve">S4_direct.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
+          <t xml:space="preserve">…ずっと黙ってたけど、そろそろ限界だよ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7706,29 +7706,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest.composed[1]</t>
+          <t xml:space="preserve">S4_silent.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
+          <t xml:space="preserve">…………（言いかけて、ひとつ息をつき、そのまま黙った）</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7738,29 +7738,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest.composed[1]</t>
+          <t xml:space="preserve">S5.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
+          <t xml:space="preserve">…まだ伸びしろはあるはずなんだ。やらせてほしい</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7770,29 +7770,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest.composed[1]</t>
+          <t xml:space="preserve">S6.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
+          <t xml:space="preserve">…次の世代に繋げたいものがあるんだ。やらせてほしい</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7802,29 +7802,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest.composed[1]</t>
+          <t xml:space="preserve">B1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
+          <t xml:space="preserve">…不注意だったね。きちんと治して、ちゃんと戻るよ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7834,29 +7834,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
+          <t xml:space="preserve">…無理に合わせても仕方ないからね。整理してもらえると助かるよ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7866,29 +7866,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
+          <t xml:space="preserve">…迷惑はかけたくないんだけどね。うまくいかないものだね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7898,29 +7898,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">B4_brand.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
+          <t xml:space="preserve">…先方のイメージを大事にね。…しっかり務めるよ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">B4_cm.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
+          <t xml:space="preserve">…ちゃんとやるよ。恥ずかしくない仕事をしたいからね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7962,29 +7962,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">B4_fan.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
+          <t xml:space="preserve">…一人ひとりと、ちゃんと向き合うよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7994,29 +7994,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
+          <t xml:space="preserve">…練習しておくよ。ちゃんと歩けるようにね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8026,29 +8026,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この関係は…もう戻らないかもね</t>
+          <t xml:space="preserve">…丁寧にやるよ。せっかくの機会だからね</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8058,29 +8058,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_variety.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この距離感。…直す方法を考えないとね</t>
+          <t xml:space="preserve">…落ち着いて話せばいいよね。焦らずやるよ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8090,29 +8090,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.composed[1]</t>
+          <t xml:space="preserve">B4.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい刺激をもらってる。ありがたいね</t>
+          <t xml:space="preserve">…なるほど、私でいいんだ。悪くない話だね</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8122,29 +8122,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一緒に上を目指せる。…いい関係だ</t>
+          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8154,29 +8154,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…学ぶことは多かった。…前に進もう</t>
+          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8186,29 +8186,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…超えるべき相手が見えた。…やるしかない</t>
+          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8218,29 +8218,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この壁を越えないと先がない。…やるよ</t>
+          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8250,29 +8250,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この人が自分を高めてくれる。…感謝、でも負けない</t>
+          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8282,29 +8282,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで頑張れることに感謝してる</t>
+          <t xml:space="preserve">…終わった件だよ。…片付けきれてないのは、私の方か</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8314,29 +8314,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力を尽くしてきたつもりだ。…でも、もう</t>
+          <t xml:space="preserve">…終わったって言われてる。…受け取れてないだけだよ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8346,29 +8346,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.composed[1]</t>
+          <t xml:space="preserve">draftInterest.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し不安を感じ始めてる。…気のせいだといいけど</t>
+          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8378,29 +8378,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">draftJoin.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調は終わった。…でも掴んだものがある</t>
+          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8410,29 +8410,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.composed[1]</t>
+          <t xml:space="preserve">faGreeting.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来た。最後まで、やるだけだよ</t>
+          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8442,29 +8442,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.composed[2]</t>
+          <t xml:space="preserve">faSigning.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。でも、繋いだものを最後で崩す気はない</t>
+          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8474,29 +8474,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">faWelcome.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手が誰でも、正面から。手を抜く理由がない</t>
+          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8506,29 +8506,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.composed[2]</t>
+          <t xml:space="preserve">heatSelf.fresh.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、確実に。…それが、繋ぐってことだろう</t>
+          <t xml:space="preserve">…今日はなんだか感覚が良い。こういう日を、無駄にしたくない</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8538,29 +8538,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.composed[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、片づけた。まだ立てる。手を抜く理由がない。次、来なよ</t>
+          <t xml:space="preserve">…今日は流れるだけだね。…私の頑張り方が雑なのかな</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8570,29 +8570,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.composed[2]</t>
+          <t xml:space="preserve">heatSelf.warm.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このリングは渡さない。繋ぐまで、退かないよ。次は誰だ</t>
+          <t xml:space="preserve">…積めてはいる。…厚みが出ないのが引っかかるね</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8602,29 +8602,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.composed[1]</t>
+          <t xml:space="preserve">injury.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で果たした約束だ。一人の手柄にする気はない</t>
+          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8634,29 +8634,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.composed[2]</t>
+          <t xml:space="preserve">release.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いだ道を……最後まで歩き切れた。それだけで十分</t>
+          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8666,29 +8666,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.composed[1]</t>
+          <t xml:space="preserve">rentalGreeting.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価は受け止める。だが、次は団体の勝利をもって応えたい</t>
+          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8698,29 +8698,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.composed[2]</t>
+          <t xml:space="preserve">scoutGreeting.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった。その事実を胸に刻んで……次に備える</t>
+          <t xml:space="preserve">…見込んでくれたんなら、その目を証明していこうか</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8730,29 +8730,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.composed[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ずつ、正面から。それ以外のやり方は知らない</t>
+          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8762,29 +8762,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.composed[2]</t>
+          <t xml:space="preserve">titleDefense.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界だった。だが……手を抜く選択肢は、最初からなかった</t>
+          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8794,29 +8794,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.composed[1]</t>
+          <t xml:space="preserve">titleLoss.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝できました。…みんなのおかげです</t>
+          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8826,29 +8826,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.earnest.composed[1]</t>
+          <t xml:space="preserve">titleWin.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力不足でした。…次は必ず</t>
+          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8858,29 +8858,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てた。…次もやるだけ</t>
+          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8890,29 +8890,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい経験になりました。…次に活かします</t>
+          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8922,29 +8922,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…全部出します</t>
+          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8954,29 +8954,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つずつ。…やることは変わらない</t>
+          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8986,29 +8986,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.earnest.composed[1]</t>
+          <t xml:space="preserve">earnest.composed[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでもらえたなら、応えないとね</t>
+          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
@@ -9028,19 +9028,19 @@
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力で行きます。よろしく</t>
+          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来れたのは、皆さんのおかげです。…ありがとう</t>
+          <t xml:space="preserve">…この関係は…もう戻らないかもね</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9082,29 +9082,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力でぶつかります。よろしく</t>
+          <t xml:space="preserve">…この距離感。…直す方法を考えないとね</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9114,29 +9114,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…残念です。…次は受けてほしいね</t>
+          <t xml:space="preserve">…いい刺激をもらってる。ありがたいね</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9146,29 +9146,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.earnest.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力が足りませんでした。…次までに詰めます</t>
+          <t xml:space="preserve">…一緒に上を目指せる。…いい関係だ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9178,29 +9178,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.earnest.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てました。…いい経験になりました</t>
+          <t xml:space="preserve">…学ぶことは多かった。…前に進もう</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9210,59 +9210,1147 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てました。…団体のために、やるべきことをやっただけです</t>
+          <t xml:space="preserve">…超えるべき相手が見えた。…やるしかない</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…この壁を越えないと先がない。…やるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…この人が自分を高めてくれる。…感謝、でも負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここで頑張れることに感謝してる</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…全力を尽くしてきたつもりだ。…でも、もう</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…少し不安を感じ始めてる。…気のせいだといいけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…好調は終わった。…でも掴んだものがある</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここまで来た。最後まで、やるだけだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体は重い。でも、繋いだものを最後で崩す気はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…相手が誰でも、正面から。手を抜く理由がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一戦ずつ、確実に。…それが、繋ぐってことだろう</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一人、片づけた。まだ立てる。手を抜く理由がない。次、来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…このリングは渡さない。繋ぐまで、退かないよ。次は誰だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人で果たした約束だ。一人の手柄にする気はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間が繋いだ道を……最後まで歩き切れた。それだけで十分</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">評価は受け止める。だが、次は団体の勝利をもって応えたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足りなかった。その事実を胸に刻んで……次に備える</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人ずつ、正面から。それ以外のやり方は知らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.earnest.composed[2]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体は限界だった。だが……手を抜く選択肢は、最初からなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…優勝できました。…みんなのおかげです</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…力不足でした。…次は必ず</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝てた。…次もやるだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いい経験になりました。…次に活かします</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…決勝か。…全部出します</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一つずつ。…やることは変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…選んでもらえたなら、応えないとね</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…全力で行きます。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここまで来れたのは、皆さんのおかげです。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…全力でぶつかります。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…残念です。…次は受けてほしいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…力が足りませんでした。…次までに詰めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝てました。…いい経験になりました</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝てました。…団体のために、やるべきことをやっただけです</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr" s="2">
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr" s="12">
+      <c r="D311" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.earnest.composed[1]</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr" s="2">
+      <c r="E311" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr" s="3">
+      <c r="F311" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…積み重ねてきたものが、ここに繋がった。…感謝だね</t>
         </is>
       </c>
     </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.composed[1]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…見込んでくれたんなら、その目を証明していこうか</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H279"/>
+  <autoFilter ref="A1:H313"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
@@ -364,7 +364,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -379,7 +379,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.composed[1]</t>
+          <t xml:space="preserve">atk.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -396,7 +396,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -411,7 +411,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.composed[2]</t>
+          <t xml:space="preserve">atk.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -428,7 +428,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -443,7 +443,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.composed[3]</t>
+          <t xml:space="preserve">atk.composed.earnest[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -460,7 +460,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.composed[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.earnest[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -475,7 +475,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.composed[4]</t>
+          <t xml:space="preserve">atk.composed.earnest[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -492,7 +492,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -507,7 +507,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.composed[1]</t>
+          <t xml:space="preserve">bigmove.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -524,7 +524,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -539,7 +539,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.composed[2]</t>
+          <t xml:space="preserve">bigmove.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -556,7 +556,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -571,7 +571,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.composed[3]</t>
+          <t xml:space="preserve">bigmove.composed.earnest[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -588,7 +588,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -603,7 +603,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.composed[1]</t>
+          <t xml:space="preserve">climax.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -620,7 +620,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -635,7 +635,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.composed[2]</t>
+          <t xml:space="preserve">climax.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -652,7 +652,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.earnest.composed[1]</t>
+          <t xml:space="preserve">badWinner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -684,7 +684,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -699,7 +699,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.earnest.composed[1]</t>
+          <t xml:space="preserve">goodWinner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -716,7 +716,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -731,7 +731,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest.composed[1]</t>
+          <t xml:space="preserve">competition_won.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -748,7 +748,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -763,7 +763,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest.composed[1]</t>
+          <t xml:space="preserve">direct.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -780,7 +780,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -795,7 +795,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest.composed[1]</t>
+          <t xml:space="preserve">fa_signing.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -812,7 +812,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.composed.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.earnest.hit[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -827,7 +827,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed.hit[1]</t>
+          <t xml:space="preserve">composed.earnest.hit[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -844,7 +844,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.composed.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.earnest.hit[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -859,7 +859,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed.hit[2]</t>
+          <t xml:space="preserve">composed.earnest.hit[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -876,7 +876,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.composed.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.earnest.win[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -891,7 +891,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed.win[1]</t>
+          <t xml:space="preserve">composed.earnest.win[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -908,7 +908,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.composed.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.earnest.win[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -923,7 +923,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed.win[2]</t>
+          <t xml:space="preserve">composed.earnest.win[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -940,7 +940,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -955,7 +955,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -972,7 +972,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -987,7 +987,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1004,7 +1004,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.composed[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[3]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1036,7 +1036,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1068,7 +1068,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1100,7 +1100,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.composed[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[3]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1132,7 +1132,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1164,7 +1164,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1196,7 +1196,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.composed[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[3]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1228,7 +1228,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1260,7 +1260,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1292,7 +1292,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.composed[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[3]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1324,7 +1324,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1356,7 +1356,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1388,7 +1388,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1420,7 +1420,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1452,7 +1452,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.earnest.composed[1]</t>
+          <t xml:space="preserve">ahead.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1484,7 +1484,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.earnest.composed[1]</t>
+          <t xml:space="preserve">behind.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1516,7 +1516,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.composed[1]</t>
+          <t xml:space="preserve">loser.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1548,7 +1548,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.composed[1]</t>
+          <t xml:space="preserve">winner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1580,7 +1580,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.composed[1]</t>
+          <t xml:space="preserve">loser.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1612,7 +1612,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.composed[1]</t>
+          <t xml:space="preserve">winner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1644,7 +1644,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1676,7 +1676,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.composed[1]</t>
+          <t xml:space="preserve">defender.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1708,7 +1708,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1740,7 +1740,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.composed[1]</t>
+          <t xml:space="preserve">defender.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1772,7 +1772,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1804,7 +1804,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.composed[1]</t>
+          <t xml:space="preserve">defender.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1836,7 +1836,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.earnest.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1868,7 +1868,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.earnest.composed[1]</t>
+          <t xml:space="preserve">fateDefender.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1900,7 +1900,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1932,7 +1932,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1964,7 +1964,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.earnest.composed[1]</t>
+          <t xml:space="preserve">fateLoser.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1996,7 +1996,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.earnest.composed[1]</t>
+          <t xml:space="preserve">fateWinner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2028,7 +2028,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.composed[1]</t>
+          <t xml:space="preserve">loser.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2060,7 +2060,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.composed[1]</t>
+          <t xml:space="preserve">winner.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2092,7 +2092,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2124,7 +2124,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2156,7 +2156,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.earnest.composed[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.earnest.composed[1]</t>
+          <t xml:space="preserve">awakening.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2956,7 +2956,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest.composed[1]</t>
+          <t xml:space="preserve">accepted.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2988,7 +2988,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest.composed[2]</t>
+          <t xml:space="preserve">accepted.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3020,7 +3020,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest.composed[1]</t>
+          <t xml:space="preserve">defended.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3052,7 +3052,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest.composed[2]</t>
+          <t xml:space="preserve">defended.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3084,7 +3084,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest.composed[1]</t>
+          <t xml:space="preserve">defense_failed.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3116,7 +3116,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest.composed[2]</t>
+          <t xml:space="preserve">defense_failed.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3148,7 +3148,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.earnest.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.earnest.composed[1]</t>
+          <t xml:space="preserve">default.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3180,7 +3180,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">former_champ.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3212,7 +3212,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.earnest.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.earnest.composed[1]</t>
+          <t xml:space="preserve">heel.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3244,7 +3244,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.earnest.composed[1]</t>
+          <t xml:space="preserve">high_trust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3276,7 +3276,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3308,7 +3308,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_heel.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3340,7 +3340,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3372,7 +3372,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3404,7 +3404,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.earnest.composed[1]</t>
+          <t xml:space="preserve">accept_winless.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3436,7 +3436,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.earnest.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3468,7 +3468,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.earnest.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3500,7 +3500,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.earnest.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3532,7 +3532,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3564,7 +3564,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.earnest.composed[1]</t>
+          <t xml:space="preserve">A1_champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3596,7 +3596,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.earnest.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3628,7 +3628,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.earnest.composed[1]</t>
+          <t xml:space="preserve">A3_heel.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3660,7 +3660,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.earnest.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3692,7 +3692,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.earnest.composed[1]</t>
+          <t xml:space="preserve">B1_young.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3724,7 +3724,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.earnest.composed[1]</t>
+          <t xml:space="preserve">B2_prime.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3756,7 +3756,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.earnest.composed[1]</t>
+          <t xml:space="preserve">B3_older.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3788,7 +3788,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3820,7 +3820,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3852,7 +3852,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.earnest.composed[1]</t>
+          <t xml:space="preserve">raise_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3884,7 +3884,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.earnest.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3916,7 +3916,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.earnest.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3948,7 +3948,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest.composed[1]</t>
+          <t xml:space="preserve">raise_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3980,7 +3980,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.earnest.composed[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4012,7 +4012,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.composed[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4044,7 +4044,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.composed[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.composed[2]</t>
+          <t xml:space="preserve">sudden_departure.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4076,7 +4076,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.earnest.composed[1]</t>
+          <t xml:space="preserve">transfer_listen.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4108,7 +4108,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest.composed[1]</t>
+          <t xml:space="preserve">transfer_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4140,7 +4140,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.earnest.composed[1]</t>
+          <t xml:space="preserve">transfer_release.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4172,7 +4172,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.earnest.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4204,7 +4204,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.earnest.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_success.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4236,7 +4236,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.earnest.composed[1]</t>
+          <t xml:space="preserve">blocked.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4269,7 +4269,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.earnest.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.earnest.composed[1]</t>
+          <t xml:space="preserve">fail.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4302,7 +4302,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.earnest.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.earnest.composed[1]</t>
+          <t xml:space="preserve">start.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4335,7 +4335,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.earnest.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.earnest.composed[1]</t>
+          <t xml:space="preserve">success.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -5616,7 +5616,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5648,7 +5648,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5680,7 +5680,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.earnest.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.earnest.composed[1]</t>
+          <t xml:space="preserve">fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5712,7 +5712,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.earnest.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.earnest.composed[1]</t>
+          <t xml:space="preserve">heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5744,7 +5744,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.earnest.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.earnest.composed[1]</t>
+          <t xml:space="preserve">warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5776,7 +5776,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.earnest.composed[1]</t>
+          <t xml:space="preserve">cap_reached.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5808,7 +5808,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.earnest.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5840,7 +5840,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.earnest.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5872,7 +5872,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.earnest.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5904,7 +5904,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.earnest.composed[1]</t>
+          <t xml:space="preserve">pop_growth.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5936,7 +5936,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.earnest.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.earnest.composed[1]</t>
+          <t xml:space="preserve">pop_star.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5968,7 +5968,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6000,7 +6000,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6032,7 +6032,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6064,7 +6064,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest.composed[1]</t>
+          <t xml:space="preserve">defeat.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6096,7 +6096,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.earnest.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6128,7 +6128,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.earnest.composed[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6160,7 +6160,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.earnest.composed[1]</t>
+          <t xml:space="preserve">penalty_end.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6192,7 +6192,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">bestMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6224,7 +6224,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.composed[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6256,7 +6256,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6288,7 +6288,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest.composed[1]</t>
+          <t xml:space="preserve">mvp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6320,7 +6320,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.earnest.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.earnest.composed[1]</t>
+          <t xml:space="preserve">rookie.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6352,7 +6352,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6384,7 +6384,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6416,7 +6416,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.composed[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[3]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6448,7 +6448,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6480,7 +6480,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.composed[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[2]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6512,7 +6512,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.composed[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[3]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6544,7 +6544,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest.composed[1]</t>
+          <t xml:space="preserve">N1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6576,7 +6576,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest.composed[1]</t>
+          <t xml:space="preserve">N2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6608,7 +6608,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest.composed[1]</t>
+          <t xml:space="preserve">N3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6640,7 +6640,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest.composed[1]</t>
+          <t xml:space="preserve">N4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6672,7 +6672,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest.composed[1]</t>
+          <t xml:space="preserve">N5_low.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6704,7 +6704,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest.composed[1]</t>
+          <t xml:space="preserve">N5_warning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6736,7 +6736,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6768,7 +6768,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">G1.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6800,7 +6800,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">G2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6832,7 +6832,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">G3.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6864,7 +6864,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">G4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6896,7 +6896,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">R2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6928,7 +6928,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.earnest.composed[1]</t>
+          <t xml:space="preserve">R3.modal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6960,7 +6960,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">R4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6992,7 +6992,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">R5.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7024,7 +7024,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.earnest.composed[1]</t>
+          <t xml:space="preserve">warVictory.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7056,7 +7056,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest.composed[1]</t>
+          <t xml:space="preserve">bonus.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7088,7 +7088,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest.composed[1]</t>
+          <t xml:space="preserve">camp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7120,7 +7120,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest.composed[1]</t>
+          <t xml:space="preserve">encourage_high_trust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7152,7 +7152,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest.composed[1]</t>
+          <t xml:space="preserve">encourage.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7184,7 +7184,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.earnest.composed[1]</t>
+          <t xml:space="preserve">faction_decree.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7216,7 +7216,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest.composed[1]</t>
+          <t xml:space="preserve">media.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7248,7 +7248,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest.composed[1]</t>
+          <t xml:space="preserve">party.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7280,7 +7280,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest.composed[1]</t>
+          <t xml:space="preserve">refresh_leave.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7312,7 +7312,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.earnest.composed[1]</t>
+          <t xml:space="preserve">special_treatment.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7344,7 +7344,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest.composed[1]</t>
+          <t xml:space="preserve">trainer.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7376,7 +7376,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.earnest.composed[1]</t>
+          <t xml:space="preserve">E1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7408,7 +7408,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest.composed[1]</t>
+          <t xml:space="preserve">E6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7440,7 +7440,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest.composed[1]</t>
+          <t xml:space="preserve">S_boycott.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7472,7 +7472,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest.composed[2]</t>
+          <t xml:space="preserve">S_boycott.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7504,7 +7504,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.earnest.composed[1]</t>
+          <t xml:space="preserve">S_grumble.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7536,7 +7536,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.earnest.composed[1]</t>
+          <t xml:space="preserve">S_sns.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7568,7 +7568,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest.composed[1]</t>
+          <t xml:space="preserve">S1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7600,7 +7600,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.earnest.composed[1]</t>
+          <t xml:space="preserve">S2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7632,7 +7632,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest.composed[1]</t>
+          <t xml:space="preserve">S3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7664,7 +7664,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest.composed[1]</t>
+          <t xml:space="preserve">S4_direct.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7696,7 +7696,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.earnest.composed[1]</t>
+          <t xml:space="preserve">S4_silent.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7728,7 +7728,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.earnest.composed[1]</t>
+          <t xml:space="preserve">S5.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7760,7 +7760,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest.composed[1]</t>
+          <t xml:space="preserve">S6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7792,7 +7792,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.earnest.composed[1]</t>
+          <t xml:space="preserve">B1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7824,7 +7824,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7856,7 +7856,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7888,7 +7888,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_brand.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7920,7 +7920,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_cm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7952,7 +7952,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_fan.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7984,7 +7984,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8016,7 +8016,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8048,7 +8048,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.earnest.composed[1]</t>
+          <t xml:space="preserve">B4_variety.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8080,7 +8080,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.earnest.composed[1]</t>
+          <t xml:space="preserve">B4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8112,7 +8112,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8144,7 +8144,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8176,7 +8176,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8208,7 +8208,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8240,7 +8240,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8272,7 +8272,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.earnest.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8304,7 +8304,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.earnest.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8336,7 +8336,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest.composed[1]</t>
+          <t xml:space="preserve">draftInterest.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8368,7 +8368,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.composed[1]</t>
+          <t xml:space="preserve">draftJoin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8400,7 +8400,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.earnest.composed[1]</t>
+          <t xml:space="preserve">faGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8432,7 +8432,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest.composed[1]</t>
+          <t xml:space="preserve">faSigning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8464,7 +8464,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest.composed[1]</t>
+          <t xml:space="preserve">faWelcome.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8496,7 +8496,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.earnest.composed[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8528,7 +8528,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.earnest.composed[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8560,7 +8560,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.earnest.composed[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8592,7 +8592,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.composed[1]</t>
+          <t xml:space="preserve">injury.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8624,7 +8624,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.composed[1]</t>
+          <t xml:space="preserve">release.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8656,7 +8656,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest.composed[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8688,7 +8688,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.earnest.composed[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8720,7 +8720,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest.composed[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8752,7 +8752,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest.composed[1]</t>
+          <t xml:space="preserve">titleDefense.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8784,7 +8784,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest.composed[1]</t>
+          <t xml:space="preserve">titleLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8816,7 +8816,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8848,7 +8848,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8880,7 +8880,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8912,7 +8912,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8944,7 +8944,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8976,7 +8976,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9008,7 +9008,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9392,7 +9392,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9424,7 +9424,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.composed[1]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9456,7 +9456,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.composed[2]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9488,7 +9488,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9520,7 +9520,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.composed[2]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9552,7 +9552,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.composed[1]</t>
+          <t xml:space="preserve">survivor.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9584,7 +9584,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.composed[2]</t>
+          <t xml:space="preserve">survivor.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9616,7 +9616,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.composed[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9648,7 +9648,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.composed[2]</t>
+          <t xml:space="preserve">champion.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9680,7 +9680,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.composed[1]</t>
+          <t xml:space="preserve">defiant.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9712,7 +9712,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.composed[2]</t>
+          <t xml:space="preserve">defiant.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9744,7 +9744,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.composed[1]</t>
+          <t xml:space="preserve">gauntlet.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9776,7 +9776,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.composed[2]</t>
+          <t xml:space="preserve">gauntlet.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9808,7 +9808,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.earnest.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.composed[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9840,7 +9840,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.earnest.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.earnest.composed[1]</t>
+          <t xml:space="preserve">postLose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9872,7 +9872,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.earnest.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.earnest.composed[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9904,7 +9904,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.earnest.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.earnest.composed[1]</t>
+          <t xml:space="preserve">postWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9936,7 +9936,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.earnest.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.composed[1]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9968,7 +9968,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.composed[1]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10000,7 +10000,7 @@
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.earnest.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.earnest.composed[1]</t>
+          <t xml:space="preserve">summon.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10032,7 +10032,7 @@
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10064,7 +10064,7 @@
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10096,7 +10096,7 @@
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.earnest.composed[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10128,7 +10128,7 @@
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.earnest.composed[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10160,7 +10160,7 @@
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.earnest.composed[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.earnest.composed[1]</t>
+          <t xml:space="preserve">result_lose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10192,7 +10192,7 @@
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.earnest.composed[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.earnest.composed[1]</t>
+          <t xml:space="preserve">result_win.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10224,7 +10224,7 @@
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10256,7 +10256,7 @@
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.earnest.composed[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.earnest.composed[1]</t>
+          <t xml:space="preserve">fighter.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10288,7 +10288,7 @@
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10320,7 +10320,7 @@
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest.composed[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{partner}、ごめん。あたしの力不足だ。</t>
+          <t xml:space="preserve">…{partner}、ごめん。私の力不足だ。</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。…わがままを通した挙句、この結果です。申し訳ありません。</t>
+          <t xml:space="preserve">負けました。…無理を通させてもらったのに、この結果です。次は必ず持ち帰ります。</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗です。…社長の判断を、無駄にしました。</t>
+          <t xml:space="preserve">完敗です。…この経験は、必ず勝ちで返してみせます。</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すみません。頼み込んだのは自分なのに、勝てませんでした。</t>
+          <t xml:space="preserve">…頼み込んだ以上は勝つつもりでした。この悔しさ、糧にしてみせます。</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受けておいて、この結果か。情けない。</t>
+          <t xml:space="preserve">……受けたからには勝ちたかった。この悔しさ、忘れない。</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けは、わたしのものだ。持って帰るよ。</t>
+          <t xml:space="preserve">……負けは、私のものだ。持って帰るよ。</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。立場をわきまえず、恥ずかしい限りです。</t>
+          <t xml:space="preserve">…申し訳ありません。少し先走りました。次は落ち着いて言葉を選びます。</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6217,14 +6217,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、あの試合で全部出せた。それだけだよ</t>
+          <t xml:space="preserve">一人ひとりの力が重なって、この優勝になった。</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[1]</t>
+          <t xml:space="preserve">bestMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6249,14 +6249,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…毎試合、ベストを出す。それが王者の仕事だろうね</t>
+          <t xml:space="preserve">…積み重ねてきたものが、あの試合で全部出せた。それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.earnest[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6281,14 +6281,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩たちへ。…焦らなくていい。やるべきことをやれば、ちゃんと届くから</t>
+          <t xml:space="preserve">…毎試合、ベストを出す。それが王者の仕事だろうね</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.earnest[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6313,14 +6313,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…毎日の積み重ねが形になった。…ここで満足はしないけどね</t>
+          <t xml:space="preserve">後輩たちへ。…焦らなくていい。やるべきことをやれば、ちゃんと届くから</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.earnest[1]</t>
+          <t xml:space="preserve">mvp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6345,14 +6345,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やることはやってきた。この賞が証明してくれたかな</t>
+          <t xml:space="preserve">…毎日の積み重ねが形になった。…ここで満足はしないけどね</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">rookie.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6377,14 +6377,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングで、積み重ねてきたすべてを出します</t>
+          <t xml:space="preserve">…やることはやってきた。この賞が証明してくれたかな</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[2]</t>
+          <t xml:space="preserve">springTagChampion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6409,14 +6409,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">準備は、万全です</t>
+          <t xml:space="preserve">二人で交わした約束を守れたことが、一番うれしい。</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[3]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6441,14 +6441,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦、絶対に勝ちます</t>
+          <t xml:space="preserve">ドームのリングで、積み重ねてきたすべてを出します</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6473,14 +6473,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員達成。事実を、しっかり受け止めます</t>
+          <t xml:space="preserve">準備は、万全です</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[2]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の声援、次への糧とします</t>
+          <t xml:space="preserve">この一戦、絶対に勝ちます</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[3]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精進を続けます。これで終わりではない</t>
+          <t xml:space="preserve">満員達成。事実を、しっかり受け止めます</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…地道にやるのが一番だよ。急がず行こう</t>
+          <t xml:space="preserve">お客様の声援、次への糧とします</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人がいると、自然と力が出るね</t>
+          <t xml:space="preserve">精進を続けます。これで終わりではない</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.earnest[1]</t>
+          <t xml:space="preserve">N1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6633,14 +6633,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休めば大丈夫。焦ることはないよ</t>
+          <t xml:space="preserve">…地道にやるのが一番だよ。急がず行こう</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.earnest[1]</t>
+          <t xml:space="preserve">N2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6665,14 +6665,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなの声、ちゃんと届いてるよ。ありがたいね</t>
+          <t xml:space="preserve">…あの人がいると、自然と力が出るね</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.earnest[1]</t>
+          <t xml:space="preserve">N3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6697,14 +6697,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嫌いになったわけじゃない。ただ……ね</t>
+          <t xml:space="preserve">…少し休めば大丈夫。焦ることはないよ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.earnest[1]</t>
+          <t xml:space="preserve">N4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6729,14 +6729,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何かが噛み合わない。…まあ、そういう時期もあるか</t>
+          <t xml:space="preserve">…みんなの声、ちゃんと届いてるよ。ありがたいね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">N5_low.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6761,14 +6761,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで積み重ねてきたものが、繋がった</t>
+          <t xml:space="preserve">…嫌いになったわけじゃない。ただ……ね</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…結果で示すしかないか</t>
+          <t xml:space="preserve">…何かが噛み合わない。…まあ、そういう時期もあるか</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6825,14 +6825,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正当な評価だろうね。…でも、自分もまだ</t>
+          <t xml:space="preserve">…ここで積み重ねてきたものが、繋がった</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">G1.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6857,14 +6857,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…焦ってはいない。…でも、待つのも限度がある</t>
+          <t xml:space="preserve">…結果で示すしかないか</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">G2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6889,14 +6889,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる。…いつでもね</t>
+          <t xml:space="preserve">…正当な評価だろうね。…でも、自分もまだ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">G3.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6921,14 +6921,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し歩み寄った方がいいのかな</t>
+          <t xml:space="preserve">…焦ってはいない。…でも、待つのも限度がある</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.composed.earnest[1]</t>
+          <t xml:space="preserve">G4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6953,14 +6953,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{name2}。…ありがとう。…元気でね</t>
+          <t xml:space="preserve">…準備はできてる。…いつでもね</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">R2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6985,14 +6985,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやった。…それだけ</t>
+          <t xml:space="preserve">…もう少し歩み寄った方がいいのかな</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">R3.modal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7017,14 +7017,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足りないか。…次までに詰めるよ</t>
+          <t xml:space="preserve">…{name2}。…ありがとう。…元気でね</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">R4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなの分も、背負えた。…よかった</t>
+          <t xml:space="preserve">…やるべきことをやった。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7066,29 +7066,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.composed.earnest[1]</t>
+          <t xml:space="preserve">R5.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいね。次で応えるよ</t>
+          <t xml:space="preserve">…まだ足りないか。…次までに詰めるよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7098,29 +7098,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.composed.earnest[1]</t>
+          <t xml:space="preserve">warVictory.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなでやれるのはいいね。じっくり行こう</t>
+          <t xml:space="preserve">…みんなの分も、背負えた。…よかった</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.composed.earnest[1]</t>
+          <t xml:space="preserve">bonus.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7145,14 +7145,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと見てくれてたんだ。…ありがとう。応えるよ</t>
+          <t xml:space="preserve">…ありがたいね。次で応えるよ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.composed.earnest[1]</t>
+          <t xml:space="preserve">camp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7177,14 +7177,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…その言葉、ありがたいよ。もう少し踏ん張ってみる</t>
+          <t xml:space="preserve">…みんなでやれるのはいいね。じっくり行こう</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.earnest[1]</t>
+          <t xml:space="preserve">encourage_high_trust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……どこで間違えたのかは、自分で考えるよ</t>
+          <t xml:space="preserve">…ずっと見てくれてたんだ。…ありがとう。応えるよ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.composed.earnest[1]</t>
+          <t xml:space="preserve">encourage.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7241,14 +7241,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつも通りやればいいよ。大丈夫</t>
+          <t xml:space="preserve">…その言葉、ありがたいよ。もう少し踏ん張ってみる</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.composed.earnest[1]</t>
+          <t xml:space="preserve">faction_decree.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7273,14 +7273,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お疲れ様。こういう時間があるから、また頑張れるね</t>
+          <t xml:space="preserve">……どこで間違えたのかは、自分で考えるよ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.composed.earnest[1]</t>
+          <t xml:space="preserve">media.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7305,14 +7305,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、たまには休むのも大事だよね。ありがとう</t>
+          <t xml:space="preserve">…いつも通りやればいいよ。大丈夫</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.composed.earnest[1]</t>
+          <t xml:space="preserve">party.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7337,14 +7337,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまでしてくれるんだ。早く戻って返すよ</t>
+          <t xml:space="preserve">…お疲れ様。こういう時間があるから、また頑張れるね</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.composed.earnest[1]</t>
+          <t xml:space="preserve">refresh_leave.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7369,14 +7369,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいね。全部吸収させてもらうよ</t>
+          <t xml:space="preserve">…まあ、たまには休むのも大事だよね。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.earnest[1]</t>
+          <t xml:space="preserve">special_treatment.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…緊張はしないよ。いつも通りやればいい</t>
+          <t xml:space="preserve">…そこまでしてくれるんだ。早く戻って返すよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.earnest[1]</t>
+          <t xml:space="preserve">trainer.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…義理があるから断ったよ。でも、一応報告だけね</t>
+          <t xml:space="preserve">…ありがたいね。全部吸収させてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.earnest[1]</t>
+          <t xml:space="preserve">E1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7465,14 +7465,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すまない。今日はどうにも体が動かなくてさ</t>
+          <t xml:space="preserve">…緊張はしないよ。いつも通りやればいい</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.earnest[2]</t>
+          <t xml:space="preserve">E6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7497,14 +7497,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…集中できないんだ。…悪いね</t>
+          <t xml:space="preserve">…義理があるから断ったよ。でも、一応報告だけね</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7529,14 +7529,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「…このままでいいのかな」と、後輩相手に珍しく弱音を漏らしている）</t>
+          <t xml:space="preserve">…すまない。今日はどうにも体が動かなくてさ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7561,14 +7561,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「…私はここで必要とされてるのかな」と、珍しく率直な投稿）</t>
+          <t xml:space="preserve">…集中できないんだ。…悪いね</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.earnest[1]</t>
+          <t xml:space="preserve">S_grumble.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる。あとはチャンスだけだよ</t>
+          <t xml:space="preserve">（「…このままでいいのかな」と、後輩相手に珍しく弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.earnest[1]</t>
+          <t xml:space="preserve">S_sns.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7625,14 +7625,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人を越えないと先に進めない。頼むよ</t>
+          <t xml:space="preserve">（SNSに「…私はここで必要とされてるのかな」と、珍しく率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.earnest[1]</t>
+          <t xml:space="preserve">S1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7657,14 +7657,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無理したくないんだ。少し休ませてもらえるかな</t>
+          <t xml:space="preserve">…準備はできてる。あとはチャンスだけだよ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.earnest[1]</t>
+          <t xml:space="preserve">S2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7689,14 +7689,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと黙ってたけど、そろそろ限界だよ</t>
+          <t xml:space="preserve">…あの人を越えないと先に進めない。頼むよ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.earnest[1]</t>
+          <t xml:space="preserve">S3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7721,14 +7721,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（言いかけて、ひとつ息をつき、そのまま黙った）</t>
+          <t xml:space="preserve">…無理したくないんだ。少し休ませてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ伸びしろはあるはずなんだ。やらせてほしい</t>
+          <t xml:space="preserve">…ずっと黙ってたけど、そろそろ限界だよ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.earnest[1]</t>
+          <t xml:space="preserve">S4_silent.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7785,14 +7785,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次の世代に繋げたいものがあるんだ。やらせてほしい</t>
+          <t xml:space="preserve">…………（言いかけて、ひとつ息をつき、そのまま黙った）</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.earnest[1]</t>
+          <t xml:space="preserve">S5.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7817,14 +7817,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…不注意だったね。きちんと治して、ちゃんと戻るよ</t>
+          <t xml:space="preserve">…まだ伸びしろはあるはずなんだ。やらせてほしい</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.earnest[1]</t>
+          <t xml:space="preserve">S6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無理に合わせても仕方ないからね。整理してもらえると助かるよ</t>
+          <t xml:space="preserve">…次の世代に繋げたいものがあるんだ。やらせてほしい</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.earnest[1]</t>
+          <t xml:space="preserve">B1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7881,14 +7881,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…迷惑はかけたくないんだけどね。うまくいかないものだね</t>
+          <t xml:space="preserve">…不注意だったね。きちんと治して、ちゃんと戻るよ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7913,14 +7913,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…先方のイメージを大事にね。…しっかり務めるよ</t>
+          <t xml:space="preserve">…無理に合わせても仕方ないからね。整理してもらえると助かるよ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7945,14 +7945,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちゃんとやるよ。恥ずかしくない仕事をしたいからね</t>
+          <t xml:space="preserve">…迷惑はかけたくないんだけどね。うまくいかないものだね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.earnest[1]</t>
+          <t xml:space="preserve">B4_brand.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人ひとりと、ちゃんと向き合うよ</t>
+          <t xml:space="preserve">…先方のイメージを大事にね。…しっかり務めるよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.earnest[1]</t>
+          <t xml:space="preserve">B4_cm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8009,14 +8009,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…練習しておくよ。ちゃんと歩けるようにね</t>
+          <t xml:space="preserve">…ちゃんとやるよ。恥ずかしくない仕事をしたいからね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.earnest[1]</t>
+          <t xml:space="preserve">B4_fan.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…丁寧にやるよ。せっかくの機会だからね</t>
+          <t xml:space="preserve">…一人ひとりと、ちゃんと向き合うよ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.earnest[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8073,14 +8073,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…落ち着いて話せばいいよね。焦らずやるよ</t>
+          <t xml:space="preserve">…練習しておくよ。ちゃんと歩けるようにね</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.earnest[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8105,14 +8105,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、私でいいんだ。悪くない話だね</t>
+          <t xml:space="preserve">…丁寧にやるよ。せっかくの機会だからね</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8122,29 +8122,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">B4_variety.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
+          <t xml:space="preserve">…落ち着いて話せばいいよね。焦らずやるよ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8154,29 +8154,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">B4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
+          <t xml:space="preserve">…なるほど、私でいいんだ。悪くない話だね</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
@@ -8201,14 +8201,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
+          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
@@ -8233,14 +8233,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
+          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
@@ -8265,14 +8265,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
+          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8297,14 +8297,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった件だよ。…片付けきれてないのは、私の方か</t>
+          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8329,14 +8329,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わったって言われてる。…受け取れてないだけだよ</t>
+          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8361,14 +8361,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
+          <t xml:space="preserve">…終わった件だよ。…片付けきれてないのは、私の方か</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8393,14 +8393,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
+          <t xml:space="preserve">…終わったって言われてる。…受け取れてないだけだよ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">draftInterest.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8425,14 +8425,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
+          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8457,14 +8457,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
+          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.earnest[1]</t>
+          <t xml:space="preserve">faGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8489,14 +8489,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
+          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.composed.earnest[1]</t>
+          <t xml:space="preserve">faSigning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8521,14 +8521,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日はなんだか感覚が良い。こういう日を、無駄にしたくない</t>
+          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.composed.earnest[1]</t>
+          <t xml:space="preserve">faWelcome.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8553,14 +8553,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は流れるだけだね。…私の頑張り方が雑なのかな</t>
+          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.composed.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8585,14 +8585,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積めてはいる。…厚みが出ないのが引っかかるね</t>
+          <t xml:space="preserve">…今日はなんだか感覚が良い。こういう日を、無駄にしたくない</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8617,14 +8617,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
+          <t xml:space="preserve">…今日は流れるだけだね。…私の頑張り方が雑なのかな</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
+          <t xml:space="preserve">…積めてはいる。…厚みが出ないのが引っかかるね</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">injury.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8681,14 +8681,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
+          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">release.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8713,14 +8713,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見込んでくれたんなら、その目を証明していこうか</t>
+          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.earnest[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8745,14 +8745,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
+          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.earnest[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8777,14 +8777,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
+          <t xml:space="preserve">…見込んでくれたんなら、その目を証明していこうか</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.earnest[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8809,14 +8809,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
+          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.earnest[1]</t>
+          <t xml:space="preserve">titleDefense.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
+          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">titleLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8873,14 +8873,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
+          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">titleWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8905,14 +8905,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
+          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
@@ -8937,14 +8937,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
+          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
@@ -8969,14 +8969,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
+          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
@@ -9001,14 +9001,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
+          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
@@ -9033,14 +9033,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
+          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この関係は…もう戻らないかもね</t>
+          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9082,29 +9082,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この距離感。…直す方法を考えないとね</t>
+          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9129,14 +9129,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい刺激をもらってる。ありがたいね</t>
+          <t xml:space="preserve">…この関係は…もう戻らないかもね</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9161,14 +9161,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一緒に上を目指せる。…いい関係だ</t>
+          <t xml:space="preserve">…この距離感。…直す方法を考えないとね</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9193,14 +9193,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…学ぶことは多かった。…前に進もう</t>
+          <t xml:space="preserve">…いい刺激をもらってる。ありがたいね</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9225,14 +9225,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…超えるべき相手が見えた。…やるしかない</t>
+          <t xml:space="preserve">…一緒に上を目指せる。…いい関係だ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9257,14 +9257,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この壁を越えないと先がない。…やるよ</t>
+          <t xml:space="preserve">…学ぶことは多かった。…前に進もう</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.composed[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9289,14 +9289,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この人が自分を高めてくれる。…感謝、でも負けない</t>
+          <t xml:space="preserve">…超えるべき相手が見えた。…やるしかない</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.composed[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで頑張れることに感謝してる</t>
+          <t xml:space="preserve">…この壁を越えないと先がない。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.composed[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9353,14 +9353,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力を尽くしてきたつもりだ。…でも、もう</t>
+          <t xml:space="preserve">…この人が自分を高めてくれる。…感謝、でも負けない</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.composed[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9385,14 +9385,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し不安を感じ始めてる。…気のせいだといいけど</t>
+          <t xml:space="preserve">…ここで頑張れることに感謝してる</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9417,14 +9417,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調は終わった。…でも掴んだものがある</t>
+          <t xml:space="preserve">…全力を尽くしてきたつもりだ。…でも、もう</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9434,29 +9434,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来た。最後まで、やるだけだよ</t>
+          <t xml:space="preserve">…少し不安を感じ始めてる。…気のせいだといいけど</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9466,29 +9466,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.earnest[2]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。でも、繋いだものを最後で崩す気はない</t>
+          <t xml:space="preserve">…好調は終わった。…でも掴んだものがある</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9513,14 +9513,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手が誰でも、正面から。手を抜く理由がない</t>
+          <t xml:space="preserve">…ここまで来た。最後まで、やるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.earnest[2]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9545,14 +9545,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、確実に。…それが、繋ぐってことだろう</t>
+          <t xml:space="preserve">身体は重い。でも、繋いだものを最後で崩す気はない</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.earnest[1]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9577,14 +9577,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、片づけた。まだ立てる。手を抜く理由がない。次、来なよ</t>
+          <t xml:space="preserve">…相手が誰でも、正面から。手を抜く理由がない</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.earnest[2]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9609,14 +9609,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このリングは渡さない。繋ぐまで、退かないよ。次は誰だ</t>
+          <t xml:space="preserve">一戦ずつ、確実に。…それが、繋ぐってことだろう</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[1]</t>
+          <t xml:space="preserve">survivor.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9641,14 +9641,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で果たした約束だ。一人の手柄にする気はない</t>
+          <t xml:space="preserve">…一人、片づけた。まだ立てる。手を抜く理由がない。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[2]</t>
+          <t xml:space="preserve">survivor.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9673,14 +9673,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いだ道を……最後まで歩き切れた。それだけで十分</t>
+          <t xml:space="preserve">…このリングは渡さない。繋ぐまで、退かないよ。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.earnest[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9705,14 +9705,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価は受け止める。だが、次は団体の勝利をもって応えたい</t>
+          <t xml:space="preserve">三人で果たした約束だ。一人の手柄にする気はない</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.earnest[2]</t>
+          <t xml:space="preserve">champion.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9737,14 +9737,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった。その事実を胸に刻んで……次に備える</t>
+          <t xml:space="preserve">仲間が繋いだ道を……最後まで歩き切れた。それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.earnest[1]</t>
+          <t xml:space="preserve">defiant.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ずつ、正面から。それ以外のやり方は知らない</t>
+          <t xml:space="preserve">評価は受け止める。だが、次は団体の勝利をもって応えたい</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.earnest[2]</t>
+          <t xml:space="preserve">defiant.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9801,14 +9801,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界だった。だが……手を抜く選択肢は、最初からなかった</t>
+          <t xml:space="preserve">足りなかった。その事実を胸に刻んで……次に備える</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9833,14 +9833,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝できました。…みんなのおかげです</t>
+          <t xml:space="preserve">一人ずつ、正面から。それ以外のやり方は知らない</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9865,14 +9865,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力不足でした。…次は必ず</t>
+          <t xml:space="preserve">身体は限界だった。だが……手を抜く選択肢は、最初からなかった</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.earnest[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9897,14 +9897,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てた。…次もやるだけ</t>
+          <t xml:space="preserve">…優勝できました。…みんなのおかげです</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.earnest[1]</t>
+          <t xml:space="preserve">postLose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9929,14 +9929,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい経験になりました。…次に活かします</t>
+          <t xml:space="preserve">…力不足でした。…次は必ず</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9961,14 +9961,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…全部出します</t>
+          <t xml:space="preserve">…勝てた。…次もやるだけ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">postWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つずつ。…やることは変わらない</t>
+          <t xml:space="preserve">…いい経験になりました。…次に活かします</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.earnest[1]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10025,14 +10025,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでもらえたなら、応えないとね</t>
+          <t xml:space="preserve">…決勝か。…全部出します</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10057,14 +10057,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力で行きます。よろしく</t>
+          <t xml:space="preserve">…一つずつ。…やることは変わらない</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">summon.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10089,14 +10089,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来れたのは、皆さんのおかげです。…ありがとう</t>
+          <t xml:space="preserve">…選んでもらえたなら、応えないとね</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.earnest[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
@@ -10121,14 +10121,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力でぶつかります。よろしく</t>
+          <t xml:space="preserve">…全力で行きます。よろしく</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.earnest[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
@@ -10153,14 +10153,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…残念です。…次は受けてほしいね</t>
+          <t xml:space="preserve">…ここまで来れたのは、皆さんのおかげです。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.earnest[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10185,14 +10185,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力が足りませんでした。…次までに詰めます</t>
+          <t xml:space="preserve">…全力でぶつかります。よろしく</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.earnest[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てました。…いい経験になりました</t>
+          <t xml:space="preserve">…残念です。…次は受けてほしいね</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">result_lose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10249,14 +10249,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てました。…団体のために、やるべきことをやっただけです</t>
+          <t xml:space="preserve">…力が足りませんでした。…次までに詰めます</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10266,29 +10266,29 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.earnest[1]</t>
+          <t xml:space="preserve">result_win.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ここに繋がった。…感謝だね</t>
+          <t xml:space="preserve">…勝てました。…いい経験になりました</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
@@ -10308,49 +10308,113 @@
       </c>
       <c r="E312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
+          <t xml:space="preserve">…勝てました。…団体のために、やるべきことをやっただけです</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…積み重ねてきたものが、ここに繋がった。…感謝だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr" s="2">
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr" s="12">
+      <c r="D315" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr" s="2">
+      <c r="E315" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr" s="3">
+      <c r="F315" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見込んでくれたんなら、その目を証明していこうか</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H313"/>
+  <autoFilter ref="A1:H315"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H315"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3852,7 +3852,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.composed.earnest[1]</t>
+          <t xml:space="preserve">decline_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。この評価に…恥じない結果を出します。</t>
+          <t xml:space="preserve">承知しました。評価は評価です。…下がった数字は、下がった理由ごと預かります。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.composed.earnest[1]</t>
+          <t xml:space="preserve">decline_hold.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。社長の判断なら…受け入れるよ。やれることをやる。</t>
+          <t xml:space="preserve">……その判断は、数字としては間違っています。……だから、間違いじゃなかったと言わせてください。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.composed.earnest[1]</t>
+          <t xml:space="preserve">decline_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…残念ですが…了解です。ただ…この判断は、忘れないでください。</t>
+          <t xml:space="preserve">はい。…薄々、自分でも感じていました。数字にも出ましたか。…最後まで聞かせてください。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.composed.earnest[1]</t>
+          <t xml:space="preserve">decline_strict.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3973,14 +3973,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、筋を通させてください。{tenure}{record}…落ち着いて考えた結論です。</t>
+          <t xml:space="preserve">……承知しました。筋は通っています。……ええ、通りすぎているくらいに。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.composed.earnest[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4005,14 +4005,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。ただ…このままでは、いずれ動くことになる。それだけです。</t>
+          <t xml:space="preserve">ありがとうございます。……自分の言葉どおりに扱ってもらえるのが、一番の信頼です。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.earnest[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4037,14 +4037,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。長い間、世話になったね。…でも、もうここでは続けられない。</t>
+          <t xml:space="preserve">……申し出を、断られるとは思いませんでした。……この額に、体のほうを追いつかせます。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.earnest[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.earnest[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4069,14 +4069,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと考えてきたことでね。…ここを、去ります。</t>
+          <t xml:space="preserve">社長、査定の前に。{tenure}……今の力に見合う額にしてください。それが筋だと思っています。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.composed.earnest[1]</t>
+          <t xml:space="preserve">raise_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。{record}自分なりに考えた結論でね。ここでの経験には感謝してる。…ただ、新しい場所で試したいんだ。</t>
+          <t xml:space="preserve">…ありがとうございます。この評価に…恥じない結果を出します。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.composed.earnest[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4133,14 +4133,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}ここでの時間は…悪くなかった。ただ…次に進むべきだと思ってます。</t>
+          <t xml:space="preserve">…なるほど。社長の判断なら…受け入れるよ。やれることをやる。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.composed.earnest[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。{tenure_farewell}ここで過ごした日々は…忘れないよ。{rivalry}</t>
+          <t xml:space="preserve">…残念ですが…了解です。ただ…この判断は、忘れないでください。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.composed.earnest[1]</t>
+          <t xml:space="preserve">raise_open.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…気持ちはありがたい。…ただ、これは長く考えた末の結論でね。…申し訳ない。</t>
+          <t xml:space="preserve">社長、筋を通させてください。{tenure}{record}…落ち着いて考えた結論です。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.composed.earnest[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4229,370 +4229,370 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長の誠意は…伝わりました。もう一度…やってみます。</t>
+          <t xml:space="preserve">…承知しました。ただ…このままでは、いずれ動くことになる。それだけです。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。長い間、世話になったね。…でも、もうここでは続けられない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ずっと考えてきたことでね。…ここを、去ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとう。{record}自分なりに考えた結論でね。ここでの経験には感謝してる。…ただ、新しい場所で試したいんだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}ここでの時間は…悪くなかった。ただ…次に進むべきだと思ってます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…承知しました。{tenure_farewell}ここで過ごした日々は…忘れないよ。{rivalry}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…気持ちはありがたい。…ただ、これは長く考えた末の結論でね。…申し訳ない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長の誠意は…伝わりました。もう一度…やってみます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr" s="12">
+      <c r="D130" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr" s="2">
+      <c r="E130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr" s="3">
+      <c r="F130" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…今の仲間への責任がある。
 それを放り出すわけにはいかない</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
+      <c r="D131" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="E131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F131" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…みんなを置いてはいけない。
 …ごめん</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
+      <c r="D132" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="E132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F132" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…この団体を離れるのは簡単じゃない。
 …でも、聞くだけなら</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…新しい場所で、やるべきことをやる。
 よろしく</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのメンバーのこと、いま少しお気にかけていただきたいのですが。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次の興行のメインを私たちに任せていただけないか、ご検討いただけますか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのメンバーの待遇について、一度ご検討いただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの貢献に、一言いただける機会をお願いしたいのですが。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ありがとうございます。お言葉、しっかり受け取ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、ご配慮ありがとうございます。お気持ち、しっかり受け取ります。</t>
-        </is>
-      </c>
-    </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。お預かりした以上、形にしてお返しします。</t>
+          <t xml:space="preserve">社長、私たちのメンバーのこと、いま少しお気にかけていただきたいのですが。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4649,14 +4649,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。次回、改めてお願いします。</t>
+          <t xml:space="preserve">社長、次の興行のメインを私たちに任せていただけないか、ご検討いただけますか。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4681,14 +4681,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。お気持ち、しっかり受け取ります。</t>
+          <t xml:space="preserve">社長、私たちのメンバーの待遇について、一度ご検討いただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。みんなを代表して、お礼を申し上げます。</t>
+          <t xml:space="preserve">社長、私たちの貢献に、一言いただける機会をお願いしたいのですが。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。お時間を取らせてしまい、すみませんでした。</t>
+          <t xml:space="preserve">ありがとうございます。お言葉、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4777,14 +4777,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮ありがとうございます。気持ち、しっかり受け取ります。</t>
+          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。お言葉、しっかり受け取ります。</t>
+          <t xml:space="preserve">…社長、ご配慮ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4841,14 +4841,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
+          <t xml:space="preserve">ありがとうございます。お預かりした以上、形にしてお返しします。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮ありがとうございます。お気持ち、しっかり受け取ります。</t>
+          <t xml:space="preserve">…承知しました。次回、改めてお願いします。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。輪の外にいる子の気持ち、見えていませんでした。</t>
+          <t xml:space="preserve">…ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎないように気をつけます。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。みんなを代表して、お礼を申し上げます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません、配慮が足りませんでした。</t>
+          <t xml:space="preserve">…承知しました。お時間を取らせてしまい、すみませんでした。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…社長、ご配慮ありがとうございます。気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。リングの外まで持ち込んだのは行きすぎでした。</t>
+          <t xml:space="preserve">ありがとうございます。お言葉、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
+          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。少し先走りました。次は落ち着いて言葉を選びます。</t>
+          <t xml:space="preserve">…社長、ご配慮ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。お見逃しいただいた分、必ず返します。</t>
+          <t xml:space="preserve">…申し訳ありません。輪の外にいる子の気持ち、見えていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長が補ってくださる形で。</t>
+          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎないように気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。ご厚意に、甘えさせていただきます。</t>
+          <t xml:space="preserve">…申し訳ありません、配慮が足りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てます。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。チームで支えていただけると、持ち直せます。</t>
+          <t xml:space="preserve">…申し訳ありません。リングの外まで持ち込んだのは行きすぎでした。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5289,14 +5289,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の目が届いていませんでした。</t>
+          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。穏便に収まるよう努めます。</t>
+          <t xml:space="preserve">…申し訳ありません。少し先走りました。次は落ち着いて言葉を選びます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5353,14 +5353,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長に補っていただいて。</t>
+          <t xml:space="preserve">…ありがとうございます。お見逃しいただいた分、必ず返します。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5385,14 +5385,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の管理不行き届きでした。</t>
+          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長が補ってくださる形で。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（唇を結び、わずかに頭を下げた）</t>
+          <t xml:space="preserve">…ありがとうございます。ご厚意に、甘えさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5449,14 +5449,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長に拾っていただいて。</t>
+          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てます。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5481,14 +5481,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の判断が行きすぎていました。</t>
+          <t xml:space="preserve">…ありがとうございます。チームで支えていただけると、持ち直せます。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5513,14 +5513,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。責任は私が持ちます。</t>
+          <t xml:space="preserve">…申し訳ありません。私の目が届いていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5545,14 +5545,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。私が見落としていた負担を、社長に拾っていただいて。</t>
+          <t xml:space="preserve">…ありがとうございます。穏便に収まるよう努めます。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.attack.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5577,14 +5577,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">けじめを、つけさせてもらう</t>
+          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長に補っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.defend.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5609,14 +5609,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるつもりはない</t>
+          <t xml:space="preserve">…申し訳ありません。私の管理不行き届きでした。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5626,29 +5626,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ようやく。…まだ上がある</t>
+          <t xml:space="preserve">（唇を結び、わずかに頭を下げた）</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5658,29 +5658,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…あの練習が…ここで繋がった——）</t>
+          <t xml:space="preserve">…ありがとうございます。私の至らなさを、社長に拾っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日はなんだか感覚が良い。こういう日を、無駄にしたくない</t>
+          <t xml:space="preserve">…申し訳ありません。私の判断が行きすぎていました。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5722,29 +5722,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は流れるだけだね。…私の頑張り方が雑なのかな</t>
+          <t xml:space="preserve">…ありがとうございます。責任は私が持ちます。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5754,29 +5754,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.composed.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積めてはいる。…厚みが出ないのが引っかかるね</t>
+          <t xml:space="preserve">…ありがとうございます。私が見落としていた負担を、社長に拾っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.composed</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5786,29 +5786,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.composed.earnest[1]</t>
+          <t xml:space="preserve">earnest.attack.composed</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…限界か。…でもここまでの道のりは、全部本物だよ</t>
+          <t xml:space="preserve">けじめを、つけさせてもらう</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.composed</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5818,29 +5818,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.composed.earnest[1]</t>
+          <t xml:space="preserve">earnest.defend.composed</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来たけど、まだ終わりじゃない。…いや、始まりだよ</t>
+          <t xml:space="preserve">逃げるつもりはない</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.earnest[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5865,14 +5865,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやってきた成果が、ちゃんと出てるね</t>
+          <t xml:space="preserve">…積み重ねてきたものが、ようやく。…まだ上がある</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.earnest[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やれるだけのことは、やった。…でも、まだやれる</t>
+          <t xml:space="preserve">（…あの練習が…ここで繋がった——）</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.earnest[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.composed.earnest[1]</t>
+          <t xml:space="preserve">fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5929,14 +5929,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてる人がいるなら、もっと頑張らないと</t>
+          <t xml:space="preserve">…今日はなんだか感覚が良い。こういう日を、無駄にしたくない</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.earnest[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.composed.earnest[1]</t>
+          <t xml:space="preserve">heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来れたのは、見てくれた人がいたから。…恩返ししないと</t>
+          <t xml:space="preserve">…今日は流れるだけだね。…私の頑張り方が雑なのかな</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5993,14 +5993,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…道場に来ても、何も返ってこない。…そういう時期か</t>
+          <t xml:space="preserve">…積めてはいる。…厚みが出ないのが引っかかるね</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">cap_reached.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6025,14 +6025,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…闘う理由、思い出した。…もう迷わないよ</t>
+          <t xml:space="preserve">…限界か。…でもここまでの道のりは、全部本物だよ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6057,14 +6057,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…待たせた分、返していくよ。…焦らずにね</t>
+          <t xml:space="preserve">…ここまで来たけど、まだ終わりじゃない。…いや、始まりだよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.composed.earnest[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6089,14 +6089,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何が足りなかったのか。…まだ答えが出ない</t>
+          <t xml:space="preserve">…コツコツやってきた成果が、ちゃんと出てるね</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6106,12 +6106,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.composed.earnest[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6121,14 +6121,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…復帰はできた。…でもまだ、足りない</t>
+          <t xml:space="preserve">…やれるだけのことは、やった。…でも、まだやれる</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.composed.earnest[1]</t>
+          <t xml:space="preserve">pop_growth.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6153,14 +6153,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…復帰できた。…でも体は覚えてるね、あの痛みを</t>
+          <t xml:space="preserve">…見てくれてる人がいるなら、もっと頑張らないと</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.composed.earnest[1]</t>
+          <t xml:space="preserve">pop_star.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6185,14 +6185,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…怪我は治った。でも離れていた時間が…少し重い</t>
+          <t xml:space="preserve">…ここまで来れたのは、見てくれた人がいたから。…恩返ししないと</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.earnest[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ひとりの力が重なって、この優勝になった。</t>
+          <t xml:space="preserve">…道場に来ても、何も返ってこない。…そういう時期か</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、あの試合で全部出せた。それだけだよ</t>
+          <t xml:space="preserve">…闘う理由、思い出した。…もう迷わないよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…毎試合、ベストを出す。それが王者の仕事だろうね</t>
+          <t xml:space="preserve">…待たせた分、返していくよ。…焦らずにね</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6298,29 +6298,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.earnest[1]</t>
+          <t xml:space="preserve">defeat.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩たちへ。…焦らなくていい。やるべきことをやれば、ちゃんと届くから</t>
+          <t xml:space="preserve">…何が足りなかったのか。…まだ答えが出ない</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6330,29 +6330,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.earnest[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…毎日の積み重ねが形になった。…ここで満足はしないけどね</t>
+          <t xml:space="preserve">…復帰はできた。…でもまだ、足りない</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.earnest[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やることはやってきた。この賞が証明してくれたかな</t>
+          <t xml:space="preserve">…復帰できた。…でも体は覚えてるね、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.composed.earnest[1]</t>
+          <t xml:space="preserve">penalty_end.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人で交わした約束を守れたことが、一番うれしい。</t>
+          <t xml:space="preserve">…怪我は治った。でも離れていた時間が…少し重い</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6441,14 +6441,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングで、積み重ねてきたすべてを出します</t>
+          <t xml:space="preserve">一人ひとりの力が重なって、この優勝になった。</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[2]</t>
+          <t xml:space="preserve">bestMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6473,14 +6473,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">準備は、万全です</t>
+          <t xml:space="preserve">…積み重ねてきたものが、あの試合で全部出せた。それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[3]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦、絶対に勝ちます</t>
+          <t xml:space="preserve">…毎試合、ベストを出す。それが王者の仕事だろうね</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員達成。事実を、しっかり受け止めます</t>
+          <t xml:space="preserve">後輩たちへ。…焦らなくていい。やるべきことをやれば、ちゃんと届くから</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[2]</t>
+          <t xml:space="preserve">mvp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6569,14 +6569,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の声援、次への糧とします</t>
+          <t xml:space="preserve">…毎日の積み重ねが形になった。…ここで満足はしないけどね</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[3]</t>
+          <t xml:space="preserve">rookie.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6601,14 +6601,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精進を続けます。これで終わりではない</t>
+          <t xml:space="preserve">…やることはやってきた。この賞が証明してくれたかな</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.earnest[1]</t>
+          <t xml:space="preserve">springTagChampion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…地道にやるのが一番だよ。急がず行こう</t>
+          <t xml:space="preserve">二人で交わした約束を守れたことが、一番うれしい。</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人がいると、自然と力が出るね</t>
+          <t xml:space="preserve">ドームのリングで、積み重ねてきたすべてを出します</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し休めば大丈夫。焦ることはないよ</t>
+          <t xml:space="preserve">準備は、万全です</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6714,29 +6714,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなの声、ちゃんと届いてるよ。ありがたいね</t>
+          <t xml:space="preserve">この一戦、絶対に勝ちます</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6746,29 +6746,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嫌いになったわけじゃない。ただ……ね</t>
+          <t xml:space="preserve">満員達成。事実を、しっかり受け止めます</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6778,29 +6778,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[2]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何かが噛み合わない。…まあ、そういう時期もあるか</t>
+          <t xml:space="preserve">お客様の声援、次への糧とします</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.earnest[3]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[3]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで積み重ねてきたものが、繋がった</t>
+          <t xml:space="preserve">精進を続けます。これで終わりではない</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">N1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6857,14 +6857,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…結果で示すしかないか</t>
+          <t xml:space="preserve">…地道にやるのが一番だよ。急がず行こう</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">N2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6889,14 +6889,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正当な評価だろうね。…でも、自分もまだ</t>
+          <t xml:space="preserve">…あの人がいると、自然と力が出るね</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">N3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6921,14 +6921,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…焦ってはいない。…でも、待つのも限度がある</t>
+          <t xml:space="preserve">…少し休めば大丈夫。焦ることはないよ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">N4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6953,14 +6953,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる。…いつでもね</t>
+          <t xml:space="preserve">…みんなの声、ちゃんと届いてるよ。ありがたいね</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">N5_low.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6985,14 +6985,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し歩み寄った方がいいのかな</t>
+          <t xml:space="preserve">…嫌いになったわけじゃない。ただ……ね</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.composed.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7017,14 +7017,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{name2}。…ありがとう。…元気でね</t>
+          <t xml:space="preserve">…何かが噛み合わない。…まあ、そういう時期もあるか</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことをやった。…それだけ</t>
+          <t xml:space="preserve">…ここで積み重ねてきたものが、繋がった</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">G1.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7081,14 +7081,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ足りないか。…次までに詰めるよ</t>
+          <t xml:space="preserve">…結果で示すしかないか</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.composed.earnest[1]</t>
+          <t xml:space="preserve">G2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7113,14 +7113,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなの分も、背負えた。…よかった</t>
+          <t xml:space="preserve">…正当な評価だろうね。…でも、自分もまだ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7130,29 +7130,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.composed.earnest[1]</t>
+          <t xml:space="preserve">G3.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいね。次で応えるよ</t>
+          <t xml:space="preserve">…焦ってはいない。…でも、待つのも限度がある</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7162,29 +7162,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.composed.earnest[1]</t>
+          <t xml:space="preserve">G4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなでやれるのはいいね。じっくり行こう</t>
+          <t xml:space="preserve">…準備はできてる。…いつでもね</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7194,29 +7194,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.composed.earnest[1]</t>
+          <t xml:space="preserve">R2.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと見てくれてたんだ。…ありがとう。応えるよ</t>
+          <t xml:space="preserve">…もう少し歩み寄った方がいいのかな</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7226,29 +7226,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.composed.earnest[1]</t>
+          <t xml:space="preserve">R3.modal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…その言葉、ありがたいよ。もう少し踏ん張ってみる</t>
+          <t xml:space="preserve">…{name2}。…ありがとう。…元気でね</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7258,29 +7258,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.earnest[1]</t>
+          <t xml:space="preserve">R4.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……どこで間違えたのかは、自分で考えるよ</t>
+          <t xml:space="preserve">…やるべきことをやった。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7290,29 +7290,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.composed.earnest[1]</t>
+          <t xml:space="preserve">R5.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつも通りやればいいよ。大丈夫</t>
+          <t xml:space="preserve">…まだ足りないか。…次までに詰めるよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7322,29 +7322,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.composed.earnest[1]</t>
+          <t xml:space="preserve">warVictory.voice.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お疲れ様。こういう時間があるから、また頑張れるね</t>
+          <t xml:space="preserve">…みんなの分も、背負えた。…よかった</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.composed.earnest[1]</t>
+          <t xml:space="preserve">bonus.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7369,14 +7369,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、たまには休むのも大事だよね。ありがとう</t>
+          <t xml:space="preserve">…ありがたいね。次で応えるよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.composed.earnest[1]</t>
+          <t xml:space="preserve">camp.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまでしてくれるんだ。早く戻って返すよ</t>
+          <t xml:space="preserve">…みんなでやれるのはいいね。じっくり行こう</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.composed.earnest[1]</t>
+          <t xml:space="preserve">encourage_high_trust.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたいね。全部吸収させてもらうよ</t>
+          <t xml:space="preserve">…ずっと見てくれてたんだ。…ありがとう。応えるよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7450,12 +7450,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.earnest[1]</t>
+          <t xml:space="preserve">encourage.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7465,14 +7465,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…緊張はしないよ。いつも通りやればいい</t>
+          <t xml:space="preserve">…その言葉、ありがたいよ。もう少し踏ん張ってみる</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.earnest[1]</t>
+          <t xml:space="preserve">faction_decree.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7497,14 +7497,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…義理があるから断ったよ。でも、一応報告だけね</t>
+          <t xml:space="preserve">……どこで間違えたのかは、自分で考えるよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.earnest[1]</t>
+          <t xml:space="preserve">media.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7529,14 +7529,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すまない。今日はどうにも体が動かなくてさ</t>
+          <t xml:space="preserve">…いつも通りやればいいよ。大丈夫</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7546,12 +7546,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.earnest[2]</t>
+          <t xml:space="preserve">party.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7561,14 +7561,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…集中できないんだ。…悪いね</t>
+          <t xml:space="preserve">…お疲れ様。こういう時間があるから、また頑張れるね</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7578,12 +7578,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.earnest[1]</t>
+          <t xml:space="preserve">refresh_leave.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「…このままでいいのかな」と、後輩相手に珍しく弱音を漏らしている）</t>
+          <t xml:space="preserve">…まあ、たまには休むのも大事だよね。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7610,12 +7610,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.earnest[1]</t>
+          <t xml:space="preserve">special_treatment.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7625,14 +7625,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「…私はここで必要とされてるのかな」と、珍しく率直な投稿）</t>
+          <t xml:space="preserve">…そこまでしてくれるんだ。早く戻って返すよ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.earnest[1]</t>
+          <t xml:space="preserve">trainer.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7657,14 +7657,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる。あとはチャンスだけだよ</t>
+          <t xml:space="preserve">…ありがたいね。全部吸収させてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.earnest[1]</t>
+          <t xml:space="preserve">E1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7689,14 +7689,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人を越えないと先に進めない。頼むよ</t>
+          <t xml:space="preserve">…緊張はしないよ。いつも通りやればいい</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.earnest[1]</t>
+          <t xml:space="preserve">E6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7721,14 +7721,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無理したくないんだ。少し休ませてもらえるかな</t>
+          <t xml:space="preserve">…義理があるから断ったよ。でも、一応報告だけね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと黙ってたけど、そろそろ限界だよ</t>
+          <t xml:space="preserve">…すまない。今日はどうにも体が動かなくてさ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7785,14 +7785,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（言いかけて、ひとつ息をつき、そのまま黙った）</t>
+          <t xml:space="preserve">…集中できないんだ。…悪いね</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.earnest[1]</t>
+          <t xml:space="preserve">S_grumble.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7817,14 +7817,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ伸びしろはあるはずなんだ。やらせてほしい</t>
+          <t xml:space="preserve">（「…このままでいいのかな」と、後輩相手に珍しく弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.earnest[1]</t>
+          <t xml:space="preserve">S_sns.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7849,14 +7849,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次の世代に繋げたいものがあるんだ。やらせてほしい</t>
+          <t xml:space="preserve">（SNSに「…私はここで必要とされてるのかな」と、珍しく率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.earnest[1]</t>
+          <t xml:space="preserve">S1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7881,14 +7881,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…不注意だったね。きちんと治して、ちゃんと戻るよ</t>
+          <t xml:space="preserve">…準備はできてる。あとはチャンスだけだよ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7898,12 +7898,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.earnest[1]</t>
+          <t xml:space="preserve">S2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7913,14 +7913,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無理に合わせても仕方ないからね。整理してもらえると助かるよ</t>
+          <t xml:space="preserve">…あの人を越えないと先に進めない。頼むよ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.earnest[1]</t>
+          <t xml:space="preserve">S3.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7945,14 +7945,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…迷惑はかけたくないんだけどね。うまくいかないものだね</t>
+          <t xml:space="preserve">…無理したくないんだ。少し休ませてもらえるかな</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7962,12 +7962,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…先方のイメージを大事にね。…しっかり務めるよ</t>
+          <t xml:space="preserve">…ずっと黙ってたけど、そろそろ限界だよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.earnest[1]</t>
+          <t xml:space="preserve">S4_silent.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8009,14 +8009,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちゃんとやるよ。恥ずかしくない仕事をしたいからね</t>
+          <t xml:space="preserve">…………（言いかけて、ひとつ息をつき、そのまま黙った）</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.earnest[1]</t>
+          <t xml:space="preserve">S5.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人ひとりと、ちゃんと向き合うよ</t>
+          <t xml:space="preserve">…まだ伸びしろはあるはずなんだ。やらせてほしい</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.earnest[1]</t>
+          <t xml:space="preserve">S6.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8073,14 +8073,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…練習しておくよ。ちゃんと歩けるようにね</t>
+          <t xml:space="preserve">…次の世代に繋げたいものがあるんだ。やらせてほしい</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.earnest[1]</t>
+          <t xml:space="preserve">B1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8105,14 +8105,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…丁寧にやるよ。せっかくの機会だからね</t>
+          <t xml:space="preserve">…不注意だったね。きちんと治して、ちゃんと戻るよ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8137,14 +8137,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…落ち着いて話せばいいよね。焦らずやるよ</t>
+          <t xml:space="preserve">…無理に合わせても仕方ないからね。整理してもらえると助かるよ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8169,14 +8169,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、私でいいんだ。悪くない話だね</t>
+          <t xml:space="preserve">…迷惑はかけたくないんだけどね。うまくいかないものだね</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8186,29 +8186,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">B4_brand.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
+          <t xml:space="preserve">…先方のイメージを大事にね。…しっかり務めるよ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8218,29 +8218,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">B4_cm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
+          <t xml:space="preserve">…ちゃんとやるよ。恥ずかしくない仕事をしたいからね</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8250,29 +8250,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">B4_fan.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
+          <t xml:space="preserve">…一人ひとりと、ちゃんと向き合うよ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8282,29 +8282,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
+          <t xml:space="preserve">…練習しておくよ。ちゃんと歩けるようにね</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8314,29 +8314,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
+          <t xml:space="preserve">…丁寧にやるよ。せっかくの機会だからね</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8346,29 +8346,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.earnest[1]</t>
+          <t xml:space="preserve">B4_variety.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった件だよ。…片付けきれてないのは、私の方か</t>
+          <t xml:space="preserve">…落ち着いて話せばいいよね。焦らずやるよ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8378,29 +8378,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.earnest[1]</t>
+          <t xml:space="preserve">B4.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わったって言われてる。…受け取れてないだけだよ</t>
+          <t xml:space="preserve">…なるほど、私でいいんだ。悪くない話だね</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8432,7 +8432,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8464,7 +8464,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8489,14 +8489,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
+          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8521,14 +8521,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
+          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8553,14 +8553,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
+          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.composed.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8585,14 +8585,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日はなんだか感覚が良い。こういう日を、無駄にしたくない</t>
+          <t xml:space="preserve">…終わった件だよ。…片付けきれてないのは、私の方か</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.composed.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8617,14 +8617,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は流れるだけだね。…私の頑張り方が雑なのかな</t>
+          <t xml:space="preserve">…終わったって言われてる。…受け取れてないだけだよ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.composed.earnest[1]</t>
+          <t xml:space="preserve">draftInterest.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積めてはいる。…厚みが出ないのが引っかかるね</t>
+          <t xml:space="preserve">…コツコツやるタイプだ。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8681,14 +8681,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
+          <t xml:space="preserve">…選んでくれてありがとう。コツコツ頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.earnest[1]</t>
+          <t xml:space="preserve">faGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8713,14 +8713,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
+          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">faSigning.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8745,14 +8745,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
+          <t xml:space="preserve">…期待に応えるよ。…コツコツやる</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.earnest[1]</t>
+          <t xml:space="preserve">faWelcome.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8777,14 +8777,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見込んでくれたんなら、その目を証明していこうか</t>
+          <t xml:space="preserve">…コツコツやる。見ていてくれれば</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8809,14 +8809,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
+          <t xml:space="preserve">…今日はなんだか感覚が良い。こういう日を、無駄にしたくない</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
+          <t xml:space="preserve">…今日は流れるだけだね。…私の頑張り方が雑なのかな</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8873,14 +8873,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
+          <t xml:space="preserve">…積めてはいる。…厚みが出ないのが引っかかるね</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.earnest[1]</t>
+          <t xml:space="preserve">injury.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8905,14 +8905,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
+          <t xml:space="preserve">…応援に応えられなくて、ごめん。必ず戻るよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">release.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8944,7 +8944,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8976,7 +8976,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9001,14 +9001,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
+          <t xml:space="preserve">…見込んでくれたんなら、その目を証明していこうか</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9033,14 +9033,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
+          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">titleDefense.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9065,14 +9065,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
+          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">titleLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9097,14 +9097,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
+          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9114,29 +9114,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この関係は…もう戻らないかもね</t>
+          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9146,29 +9146,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この距離感。…直す方法を考えないとね</t>
+          <t xml:space="preserve">…応援してくれた人たちに、申し訳ない。次で必ず</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9178,29 +9178,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい刺激をもらってる。ありがたいね</t>
+          <t xml:space="preserve">…短い間でも精一杯やる。よろしく</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9210,29 +9210,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一緒に上を目指せる。…いい関係だ</t>
+          <t xml:space="preserve">…足りなかった。…もっと積み重ねるよ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9242,29 +9242,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…学ぶことは多かった。…前に進もう</t>
+          <t xml:space="preserve">…防衛できた。…でもまだ満足はしない</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9274,29 +9274,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…超えるべき相手が見えた。…やるしかない</t>
+          <t xml:space="preserve">…足りなかった。…一からやり直そう</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9306,29 +9306,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.composed[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この壁を越えないと先がない。…やるよ</t>
+          <t xml:space="preserve">…積み重ねてきたものが、ここに。…大切にする</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9353,14 +9353,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この人が自分を高めてくれる。…感謝、でも負けない</t>
+          <t xml:space="preserve">…この関係は…もう戻らないかもね</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9385,14 +9385,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで頑張れることに感謝してる</t>
+          <t xml:space="preserve">…この距離感。…直す方法を考えないとね</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9417,14 +9417,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力を尽くしてきたつもりだ。…でも、もう</t>
+          <t xml:space="preserve">…いい刺激をもらってる。ありがたいね</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9449,14 +9449,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し不安を感じ始めてる。…気のせいだといいけど</t>
+          <t xml:space="preserve">…一緒に上を目指せる。…いい関係だ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9481,14 +9481,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調は終わった。…でも掴んだものがある</t>
+          <t xml:space="preserve">…学ぶことは多かった。…前に進もう</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9498,29 +9498,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来た。最後まで、やるだけだよ</t>
+          <t xml:space="preserve">…超えるべき相手が見えた。…やるしかない</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9530,29 +9530,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.earnest[2]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。でも、繋いだものを最後で崩す気はない</t>
+          <t xml:space="preserve">…この壁を越えないと先がない。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9562,29 +9562,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手が誰でも、正面から。手を抜く理由がない</t>
+          <t xml:space="preserve">…この人が自分を高めてくれる。…感謝、でも負けない</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9594,29 +9594,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.earnest[2]</t>
+          <t xml:space="preserve">trust_above_75.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、確実に。…それが、繋ぐってことだろう</t>
+          <t xml:space="preserve">…ここで頑張れることに感謝してる</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9626,29 +9626,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.earnest[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、片づけた。まだ立てる。手を抜く理由がない。次、来なよ</t>
+          <t xml:space="preserve">…全力を尽くしてきたつもりだ。…でも、もう</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.composed[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9658,29 +9658,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.earnest[2]</t>
+          <t xml:space="preserve">trust_below_35.earnest.composed[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このリングは渡さない。繋ぐまで、退かないよ。次は誰だ</t>
+          <t xml:space="preserve">…少し不安を感じ始めてる。…気のせいだといいけど</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9690,29 +9690,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で果たした約束だ。一人の手柄にする気はない</t>
+          <t xml:space="preserve">…好調は終わった。…でも掴んだものがある</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[2]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9737,14 +9737,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いだ道を……最後まで歩き切れた。それだけで十分</t>
+          <t xml:space="preserve">…ここまで来た。最後まで、やるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.earnest[1]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価は受け止める。だが、次は団体の勝利をもって応えたい</t>
+          <t xml:space="preserve">身体は重い。でも、繋いだものを最後で崩す気はない</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.earnest[2]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9801,14 +9801,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった。その事実を胸に刻んで……次に備える</t>
+          <t xml:space="preserve">…相手が誰でも、正面から。手を抜く理由がない</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.earnest[1]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9833,14 +9833,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ずつ、正面から。それ以外のやり方は知らない</t>
+          <t xml:space="preserve">一戦ずつ、確実に。…それが、繋ぐってことだろう</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.earnest[2]</t>
+          <t xml:space="preserve">survivor.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9865,14 +9865,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界だった。だが……手を抜く選択肢は、最初からなかった</t>
+          <t xml:space="preserve">…一人、片づけた。まだ立てる。手を抜く理由がない。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[1]</t>
+          <t xml:space="preserve">survivor.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9897,14 +9897,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝できました。…みんなのおかげです</t>
+          <t xml:space="preserve">…このリングは渡さない。繋ぐまで、退かないよ。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.earnest[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9929,14 +9929,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力不足でした。…次は必ず</t>
+          <t xml:space="preserve">三人で果たした約束だ。一人の手柄にする気はない</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.earnest[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9961,14 +9961,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てた。…次もやるだけ</t>
+          <t xml:space="preserve">仲間が繋いだ道を……最後まで歩き切れた。それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.earnest[1]</t>
+          <t xml:space="preserve">defiant.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい経験になりました。…次に活かします</t>
+          <t xml:space="preserve">評価は受け止める。だが、次は団体の勝利をもって応えたい</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">defiant.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10025,14 +10025,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…全部出します</t>
+          <t xml:space="preserve">足りなかった。その事実を胸に刻んで……次に備える</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10057,14 +10057,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つずつ。…やることは変わらない</t>
+          <t xml:space="preserve">一人ずつ、正面から。それ以外のやり方は知らない</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10089,14 +10089,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでもらえたなら、応えないとね</t>
+          <t xml:space="preserve">身体は限界だった。だが……手を抜く選択肢は、最初からなかった</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10121,14 +10121,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力で行きます。よろしく</t>
+          <t xml:space="preserve">…優勝できました。…みんなのおかげです</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">postLose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10153,14 +10153,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来れたのは、皆さんのおかげです。…ありがとう</t>
+          <t xml:space="preserve">…力不足でした。…次は必ず</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10185,14 +10185,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力でぶつかります。よろしく</t>
+          <t xml:space="preserve">…勝てた。…次もやるだけ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">postWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…残念です。…次は受けてほしいね</t>
+          <t xml:space="preserve">…いい経験になりました。…次に活かします</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.earnest[1]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10249,14 +10249,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力が足りませんでした。…次までに詰めます</t>
+          <t xml:space="preserve">…決勝か。…全部出します</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10266,12 +10266,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.earnest[1]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10281,14 +10281,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てました。…いい経験になりました</t>
+          <t xml:space="preserve">…一つずつ。…やることは変わらない</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">summon.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10313,14 +10313,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てました。…団体のために、やるべきことをやっただけです</t>
+          <t xml:space="preserve">…選んでもらえたなら、応えないとね</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.earnest[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10330,29 +10330,29 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ここに繋がった。…感謝だね</t>
+          <t xml:space="preserve">…全力で行きます。よろしく</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
@@ -10372,49 +10372,273 @@
       </c>
       <c r="E314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
+          <t xml:space="preserve">…ここまで来れたのは、皆さんのおかげです。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…全力でぶつかります。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…残念です。…次は受けてほしいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…力が足りませんでした。…次までに詰めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝てました。…いい経験になりました</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝てました。…団体のために、やるべきことをやっただけです</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…積み重ねてきたものが、ここに繋がった。…感謝だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr" s="2">
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr" s="12">
+      <c r="D322" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr" s="2">
+      <c r="E322" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr" s="3">
+      <c r="F322" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見込んでくれたんなら、その目を証明していこうか</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H315"/>
+  <autoFilter ref="A1:H322"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H315"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9456,7 +9456,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9481,14 +9481,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調は終わった。…でも掴んだものがある</t>
+          <t xml:space="preserve">…いい試合だった。…この経験を糧にする</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9498,29 +9498,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来た。最後まで、やるだけだよ</t>
+          <t xml:space="preserve">…全てを出し切って勝てた。…これ以上はない</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9530,29 +9530,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.earnest[2]</t>
+          <t xml:space="preserve">GL-01.loss.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。でも、繋いだものを最後で崩す気はない</t>
+          <t xml:space="preserve">…負けた原因は分かってる。…次に活かす</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9562,29 +9562,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">GL-01.win.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手が誰でも、正面から。手を抜く理由がない</t>
+          <t xml:space="preserve">…勝てた。…次に繋げよう</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9594,29 +9594,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.earnest[2]</t>
+          <t xml:space="preserve">GL-02.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、確実に。…それが、繋ぐってことだろう</t>
+          <t xml:space="preserve">…一つずつ、着実に</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9626,29 +9626,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.earnest[1]</t>
+          <t xml:space="preserve">GL-03.down.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、片づけた。まだ立てる。手を抜く理由がない。次、来なよ</t>
+          <t xml:space="preserve">…少し思うところがある</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9658,29 +9658,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.earnest[2]</t>
+          <t xml:space="preserve">GL-03.up.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このリングは渡さない。繋ぐまで、退かないよ。次は誰だ</t>
+          <t xml:space="preserve">…いい環境だ。…応えないとね</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9690,29 +9690,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で果たした約束だ。一人の手柄にする気はない</t>
+          <t xml:space="preserve">…好調は終わった。…でも掴んだものがある</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[2]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9737,14 +9737,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いだ道を……最後まで歩き切れた。それだけで十分</t>
+          <t xml:space="preserve">…ここまで来た。最後まで、やるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.earnest[1]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価は受け止める。だが、次は団体の勝利をもって応えたい</t>
+          <t xml:space="preserve">身体は重い。でも、繋いだものを最後で崩す気はない</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.earnest[2]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9801,14 +9801,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった。その事実を胸に刻んで……次に備える</t>
+          <t xml:space="preserve">…相手が誰でも、正面から。手を抜く理由がない</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.earnest[1]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9833,14 +9833,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ずつ、正面から。それ以外のやり方は知らない</t>
+          <t xml:space="preserve">一戦ずつ、確実に。…それが、繋ぐってことだろう</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.earnest[2]</t>
+          <t xml:space="preserve">survivor.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9865,14 +9865,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界だった。だが……手を抜く選択肢は、最初からなかった</t>
+          <t xml:space="preserve">…一人、片づけた。まだ立てる。手を抜く理由がない。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.earnest[1]</t>
+          <t xml:space="preserve">survivor.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9897,14 +9897,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝できました。…みんなのおかげです</t>
+          <t xml:space="preserve">…このリングは渡さない。繋ぐまで、退かないよ。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.earnest[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9929,14 +9929,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力不足でした。…次は必ず</t>
+          <t xml:space="preserve">三人で果たした約束だ。一人の手柄にする気はない</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.earnest[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9961,14 +9961,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てた。…次もやるだけ</t>
+          <t xml:space="preserve">仲間が繋いだ道を……最後まで歩き切れた。それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.earnest[1]</t>
+          <t xml:space="preserve">defiant.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい経験になりました。…次に活かします</t>
+          <t xml:space="preserve">評価は受け止める。だが、次は団体の勝利をもって応えたい</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
+          <t xml:space="preserve">defiant.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10025,14 +10025,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…全部出します</t>
+          <t xml:space="preserve">足りなかった。その事実を胸に刻んで……次に備える</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10057,14 +10057,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つずつ。…やることは変わらない</t>
+          <t xml:space="preserve">一人ずつ、正面から。それ以外のやり方は知らない</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.earnest[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.composed.earnest[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10089,14 +10089,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでもらえたなら、応えないとね</t>
+          <t xml:space="preserve">身体は限界だった。だが……手を抜く選択肢は、最初からなかった</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">champion.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10121,14 +10121,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力で行きます。よろしく</t>
+          <t xml:space="preserve">…優勝できました。…みんなのおかげです</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">postLose.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10153,14 +10153,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来れたのは、皆さんのおかげです。…ありがとう</t>
+          <t xml:space="preserve">…力不足でした。…次は必ず</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10185,14 +10185,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全力でぶつかります。よろしく</t>
+          <t xml:space="preserve">…勝てた。…次もやるだけ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">postWin.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…残念です。…次は受けてほしいね</t>
+          <t xml:space="preserve">…いい経験になりました。…次に活かします</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.earnest[1]</t>
+          <t xml:space="preserve">preFinal.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10249,14 +10249,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力が足りませんでした。…次までに詰めます</t>
+          <t xml:space="preserve">…決勝か。…全部出します</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10266,12 +10266,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.earnest[1]</t>
+          <t xml:space="preserve">preMatch.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10281,14 +10281,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てました。…いい経験になりました</t>
+          <t xml:space="preserve">…一つずつ。…やることは変わらない</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.earnest[1]</t>
+          <t xml:space="preserve">summon.composed.earnest[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10313,14 +10313,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てました。…団体のために、やるべきことをやっただけです</t>
+          <t xml:space="preserve">…選んでもらえたなら、応えないとね</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.earnest[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10330,29 +10330,29 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.earnest[1]</t>
+          <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…積み重ねてきたものが、ここに繋がった。…感謝だね</t>
+          <t xml:space="preserve">…全力で行きます。よろしく</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.earnest[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.earnest[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
@@ -10372,49 +10372,273 @@
       </c>
       <c r="E314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
+          <t xml:space="preserve">…ここまで来れたのは、皆さんのおかげです。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…全力でぶつかります。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…残念です。…次は受けてほしいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…力が足りませんでした。…次までに詰めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝てました。…いい経験になりました</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝てました。…団体のために、やるべきことをやっただけです</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…積み重ねてきたものが、ここに繋がった。…感謝だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…二度目はもうない。…だから丁寧にやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.earnest[1]</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr" s="2">
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr" s="12">
+      <c r="D322" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.earnest[1]</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr" s="2">
+      <c r="E322" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr" s="3">
+      <c r="F322" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見込んでくれたんなら、その目を証明していこうか</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H315"/>
+  <autoFilter ref="A1:H322"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×真面目.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…あの人と、やらせてください。覚悟はできています。</t>
+          <t xml:space="preserve">社長。…三人で行かせてください。覚悟はできています。</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わがままを言います。あの人と、やらせてください。責任は取ります。</t>
+          <t xml:space="preserve">…わがままを言います。三人で挑ませてください。責任は取ります。</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…自分に必要な相手です。あの人と、お願いします。</t>
+          <t xml:space="preserve">社長。…今の自分に必要な相手です。三人で、お願いします。</t>
         </is>
       </c>
     </row>
